--- a/src/main/resources/espacios/Software/0 - arquitectura hexagonal.xlsx
+++ b/src/main/resources/espacios/Software/0 - arquitectura hexagonal.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1032" uniqueCount="724">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1076" uniqueCount="724">
   <si>
     <t xml:space="preserve">What is hexagonal architecture and what is its main purpose?</t>
   </si>
@@ -2282,7 +2282,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2423,6 +2423,7 @@
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
+      <c r="F1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="45.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
@@ -2431,7 +2432,7 @@
       <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2442,6 +2443,9 @@
       <c r="B3" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="F3" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="34.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
@@ -2450,7 +2454,7 @@
       <c r="B4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="0" t="s">
+      <c r="F4" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2461,6 +2465,9 @@
       <c r="B5" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="F5" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
@@ -2469,7 +2476,7 @@
       <c r="B6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="0" t="s">
+      <c r="F6" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2480,7 +2487,7 @@
       <c r="B7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="0" t="s">
+      <c r="F7" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2491,7 +2498,7 @@
       <c r="B8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F8" s="0" t="s">
+      <c r="F8" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2502,7 +2509,7 @@
       <c r="B9" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F9" s="0" t="s">
+      <c r="F9" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2513,7 +2520,7 @@
       <c r="B10" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="F10" s="0" t="s">
+      <c r="F10" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2524,7 +2531,7 @@
       <c r="B11" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F11" s="0" t="s">
+      <c r="F11" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2535,6 +2542,9 @@
       <c r="B12" s="2" t="s">
         <v>24</v>
       </c>
+      <c r="F12" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
@@ -2543,7 +2553,7 @@
       <c r="B13" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F13" s="0" t="s">
+      <c r="F13" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2554,7 +2564,7 @@
       <c r="B14" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F14" s="0" t="s">
+      <c r="F14" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2565,7 +2575,7 @@
       <c r="B15" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F15" s="0" t="s">
+      <c r="F15" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2576,7 +2586,7 @@
       <c r="B16" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F16" s="0" t="s">
+      <c r="F16" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2587,7 +2597,7 @@
       <c r="B17" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F17" s="0" t="s">
+      <c r="F17" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2598,7 +2608,7 @@
       <c r="B18" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F18" s="0" t="s">
+      <c r="F18" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2609,7 +2619,7 @@
       <c r="B19" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F19" s="0" t="s">
+      <c r="F19" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2620,6 +2630,9 @@
       <c r="B20" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="F20" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="34.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
@@ -2628,7 +2641,7 @@
       <c r="B21" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F21" s="0" t="s">
+      <c r="F21" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2639,6 +2652,9 @@
       <c r="B22" s="2" t="s">
         <v>44</v>
       </c>
+      <c r="F22" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
@@ -2647,7 +2663,7 @@
       <c r="B23" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F23" s="0" t="s">
+      <c r="F23" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2658,7 +2674,7 @@
       <c r="B24" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="F24" s="0" t="s">
+      <c r="F24" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2669,7 +2685,7 @@
       <c r="B25" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="F25" s="0" t="s">
+      <c r="F25" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2680,7 +2696,7 @@
       <c r="B26" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="F26" s="0" t="s">
+      <c r="F26" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2691,6 +2707,9 @@
       <c r="B27" s="2" t="s">
         <v>54</v>
       </c>
+      <c r="F27" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
@@ -2699,7 +2718,7 @@
       <c r="B28" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="F28" s="0" t="s">
+      <c r="F28" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2710,6 +2729,9 @@
       <c r="B29" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="F29" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
@@ -2718,7 +2740,7 @@
       <c r="B30" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F30" s="0" t="s">
+      <c r="F30" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2729,7 +2751,7 @@
       <c r="B31" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="F31" s="0" t="s">
+      <c r="F31" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2740,7 +2762,7 @@
       <c r="B32" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F32" s="0" t="s">
+      <c r="F32" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2751,6 +2773,9 @@
       <c r="B33" s="2" t="s">
         <v>66</v>
       </c>
+      <c r="F33" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
@@ -2759,7 +2784,7 @@
       <c r="B34" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="F34" s="0" t="s">
+      <c r="F34" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2770,7 +2795,7 @@
       <c r="B35" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="F35" s="0" t="s">
+      <c r="F35" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2781,7 +2806,7 @@
       <c r="B36" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="F36" s="0" t="s">
+      <c r="F36" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2792,7 +2817,7 @@
       <c r="B37" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F37" s="0" t="s">
+      <c r="F37" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2803,7 +2828,7 @@
       <c r="B38" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="F38" s="0" t="s">
+      <c r="F38" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2814,6 +2839,7 @@
       <c r="B39" s="2" t="s">
         <v>78</v>
       </c>
+      <c r="F39" s="1"/>
     </row>
     <row r="40" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
@@ -2822,7 +2848,7 @@
       <c r="B40" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="F40" s="0" t="s">
+      <c r="F40" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2833,6 +2859,9 @@
       <c r="B41" s="2" t="s">
         <v>82</v>
       </c>
+      <c r="F41" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
@@ -2841,7 +2870,7 @@
       <c r="B42" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="F42" s="0" t="s">
+      <c r="F42" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2852,6 +2881,9 @@
       <c r="B43" s="2" t="s">
         <v>86</v>
       </c>
+      <c r="F43" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="34.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
@@ -2860,7 +2892,7 @@
       <c r="B44" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="F44" s="0" t="s">
+      <c r="F44" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2871,6 +2903,9 @@
       <c r="B45" s="2" t="s">
         <v>90</v>
       </c>
+      <c r="F45" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="34.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
@@ -2879,7 +2914,7 @@
       <c r="B46" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="F46" s="0" t="s">
+      <c r="F46" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2890,6 +2925,9 @@
       <c r="B47" s="2" t="s">
         <v>94</v>
       </c>
+      <c r="F47" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
@@ -2898,7 +2936,7 @@
       <c r="B48" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="F48" s="0" t="s">
+      <c r="F48" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2909,6 +2947,9 @@
       <c r="B49" s="2" t="s">
         <v>98</v>
       </c>
+      <c r="F49" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="s">
@@ -2917,7 +2958,7 @@
       <c r="B50" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="F50" s="0" t="s">
+      <c r="F50" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2928,6 +2969,9 @@
       <c r="B51" s="2" t="s">
         <v>102</v>
       </c>
+      <c r="F51" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2" t="s">
@@ -2936,7 +2980,7 @@
       <c r="B52" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="F52" s="0" t="s">
+      <c r="F52" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2947,6 +2991,9 @@
       <c r="B53" s="2" t="s">
         <v>106</v>
       </c>
+      <c r="F53" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="54" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2" t="s">
@@ -2955,7 +3002,7 @@
       <c r="B54" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="F54" s="0" t="s">
+      <c r="F54" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2966,6 +3013,9 @@
       <c r="B55" s="2" t="s">
         <v>110</v>
       </c>
+      <c r="F55" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="56" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
@@ -2974,7 +3024,7 @@
       <c r="B56" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="F56" s="0" t="s">
+      <c r="F56" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2985,6 +3035,9 @@
       <c r="B57" s="2" t="s">
         <v>114</v>
       </c>
+      <c r="F57" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="58" customFormat="false" ht="34.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2" t="s">
@@ -2993,7 +3046,7 @@
       <c r="B58" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="F58" s="0" t="s">
+      <c r="F58" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3004,6 +3057,9 @@
       <c r="B59" s="2" t="s">
         <v>118</v>
       </c>
+      <c r="F59" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="60" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="2" t="s">
@@ -3012,7 +3068,7 @@
       <c r="B60" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="F60" s="0" t="s">
+      <c r="F60" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3023,6 +3079,9 @@
       <c r="B61" s="2" t="s">
         <v>122</v>
       </c>
+      <c r="F61" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="62" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2" t="s">
@@ -3031,7 +3090,7 @@
       <c r="B62" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="F62" s="0" t="s">
+      <c r="F62" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3042,6 +3101,9 @@
       <c r="B63" s="2" t="s">
         <v>126</v>
       </c>
+      <c r="F63" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="64" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="2" t="s">
@@ -3050,7 +3112,7 @@
       <c r="B64" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="F64" s="0" t="s">
+      <c r="F64" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3061,6 +3123,7 @@
       <c r="B65" s="2" t="s">
         <v>130</v>
       </c>
+      <c r="F65" s="1"/>
     </row>
     <row r="66" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="2" t="s">
@@ -3069,7 +3132,7 @@
       <c r="B66" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="F66" s="0" t="s">
+      <c r="F66" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3080,6 +3143,9 @@
       <c r="B67" s="2" t="s">
         <v>134</v>
       </c>
+      <c r="F67" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="68" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="2" t="s">
@@ -3088,7 +3154,7 @@
       <c r="B68" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="F68" s="0" t="s">
+      <c r="F68" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3099,6 +3165,9 @@
       <c r="B69" s="2" t="s">
         <v>138</v>
       </c>
+      <c r="F69" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="2" t="s">
@@ -3107,7 +3176,7 @@
       <c r="B70" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="F70" s="0" t="s">
+      <c r="F70" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3118,7 +3187,7 @@
       <c r="B71" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="F71" s="0" t="s">
+      <c r="F71" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3129,7 +3198,7 @@
       <c r="B72" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="F72" s="0" t="s">
+      <c r="F72" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3140,7 +3209,7 @@
       <c r="B73" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="F73" s="0" t="s">
+      <c r="F73" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3151,7 +3220,7 @@
       <c r="B74" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="F74" s="0" t="s">
+      <c r="F74" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3162,6 +3231,9 @@
       <c r="B75" s="2" t="s">
         <v>150</v>
       </c>
+      <c r="F75" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="76" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="2" t="s">
@@ -3170,7 +3242,7 @@
       <c r="B76" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="F76" s="0" t="s">
+      <c r="F76" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3190,11 +3262,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F115"/>
+  <dimension ref="A1:F85"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="147.47"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="185.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="185.36"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3205,14 +3277,14 @@
         <v>154</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="34.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
         <v>155</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3223,6 +3295,9 @@
       <c r="B3" s="3" t="s">
         <v>158</v>
       </c>
+      <c r="F3" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
@@ -3231,7 +3306,7 @@
       <c r="B4" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="F4" s="0" t="s">
+      <c r="F4" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3242,7 +3317,7 @@
       <c r="B5" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="F5" s="0" t="s">
+      <c r="F5" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3253,13 +3328,19 @@
       <c r="B6" s="3" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F6" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
         <v>165</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>166</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3269,7 +3350,7 @@
       <c r="B8" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="F8" s="0" t="s">
+      <c r="F8" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3280,7 +3361,7 @@
       <c r="B9" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="F9" s="0" t="s">
+      <c r="F9" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3291,7 +3372,7 @@
       <c r="B10" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="F10" s="0" t="s">
+      <c r="F10" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3302,7 +3383,7 @@
       <c r="B11" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="F11" s="0" t="s">
+      <c r="F11" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3313,7 +3394,7 @@
       <c r="B12" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="F12" s="0" t="s">
+      <c r="F12" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3324,7 +3405,7 @@
       <c r="B13" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="F13" s="0" t="s">
+      <c r="F13" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3335,7 +3416,7 @@
       <c r="B14" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="F14" s="0" t="s">
+      <c r="F14" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3346,7 +3427,7 @@
       <c r="B15" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="F15" s="0" t="s">
+      <c r="F15" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3357,6 +3438,9 @@
       <c r="B16" s="3" t="s">
         <v>184</v>
       </c>
+      <c r="F16" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="45.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
@@ -3365,6 +3449,9 @@
       <c r="B17" s="3" t="s">
         <v>186</v>
       </c>
+      <c r="F17" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="34.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
@@ -3373,6 +3460,9 @@
       <c r="B18" s="3" t="s">
         <v>188</v>
       </c>
+      <c r="F18" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
@@ -3381,7 +3471,7 @@
       <c r="B19" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="F19" s="0" t="s">
+      <c r="F19" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3392,7 +3482,7 @@
       <c r="B20" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="F20" s="0" t="s">
+      <c r="F20" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3403,7 +3493,7 @@
       <c r="B21" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="F21" s="0" t="s">
+      <c r="F21" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3414,6 +3504,9 @@
       <c r="B22" s="3" t="s">
         <v>196</v>
       </c>
+      <c r="F22" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
@@ -3422,27 +3515,30 @@
       <c r="B23" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="F23" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F23" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
         <v>199</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="F24" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F24" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
         <v>201</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>202</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3452,18 +3548,18 @@
       <c r="B26" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="F26" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F26" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="51.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
         <v>205</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="F27" s="0" t="s">
+      <c r="F27" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3474,7 +3570,7 @@
       <c r="B28" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="F28" s="0" t="s">
+      <c r="F28" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3485,7 +3581,7 @@
       <c r="B29" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="F29" s="0" t="s">
+      <c r="F29" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3496,7 +3592,7 @@
       <c r="B30" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="F30" s="0" t="s">
+      <c r="F30" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3507,6 +3603,9 @@
       <c r="B31" s="3" t="s">
         <v>214</v>
       </c>
+      <c r="F31" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="57.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
@@ -3515,6 +3614,9 @@
       <c r="B32" s="3" t="s">
         <v>216</v>
       </c>
+      <c r="F32" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
@@ -3531,7 +3633,7 @@
       <c r="B34" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="F34" s="0" t="s">
+      <c r="F34" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3542,7 +3644,7 @@
       <c r="B35" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="F35" s="0" t="s">
+      <c r="F35" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3553,7 +3655,7 @@
       <c r="B36" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="F36" s="0" t="s">
+      <c r="F36" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3564,7 +3666,7 @@
       <c r="B37" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="F37" s="0" t="s">
+      <c r="F37" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3575,7 +3677,7 @@
       <c r="B38" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="F38" s="0" t="s">
+      <c r="F38" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3586,7 +3688,7 @@
       <c r="B39" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="F39" s="0" t="s">
+      <c r="F39" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3597,7 +3699,7 @@
       <c r="B40" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="F40" s="0" t="s">
+      <c r="F40" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3608,7 +3710,7 @@
       <c r="B41" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="F41" s="0" t="s">
+      <c r="F41" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3619,7 +3721,7 @@
       <c r="B42" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="F42" s="0" t="s">
+      <c r="F42" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3630,6 +3732,9 @@
       <c r="B43" s="3" t="s">
         <v>237</v>
       </c>
+      <c r="F43" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="s">
@@ -3638,7 +3743,7 @@
       <c r="B44" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="F44" s="0" t="s">
+      <c r="F44" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3649,7 +3754,7 @@
       <c r="B45" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="F45" s="0" t="s">
+      <c r="F45" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3660,7 +3765,7 @@
       <c r="B46" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="F46" s="0" t="s">
+      <c r="F46" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3671,24 +3776,30 @@
       <c r="B47" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="F47" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="45.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F47" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="34.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="3" t="s">
         <v>246</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>247</v>
       </c>
-    </row>
-    <row r="49" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F48" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="3" t="s">
         <v>248</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>249</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3698,7 +3809,7 @@
       <c r="B50" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="F50" s="0" t="s">
+      <c r="F50" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3709,7 +3820,7 @@
       <c r="B51" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="F51" s="0" t="s">
+      <c r="F51" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3720,7 +3831,7 @@
       <c r="B52" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="F52" s="0" t="s">
+      <c r="F52" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3731,7 +3842,7 @@
       <c r="B53" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="F53" s="0" t="s">
+      <c r="F53" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3742,6 +3853,9 @@
       <c r="B54" s="3" t="s">
         <v>259</v>
       </c>
+      <c r="F54" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="3" t="s">
@@ -3750,27 +3864,30 @@
       <c r="B55" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="F55" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F55" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="3" t="s">
         <v>262</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="F56" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F56" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="3" t="s">
         <v>264</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>265</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3780,7 +3897,7 @@
       <c r="B58" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="F58" s="0" t="s">
+      <c r="F58" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3791,27 +3908,30 @@
       <c r="B59" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="F59" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F59" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="3" t="s">
         <v>270</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="F60" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F60" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="3" t="s">
         <v>272</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>273</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3821,18 +3941,18 @@
       <c r="B62" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="F62" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="34.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F62" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="3" t="s">
         <v>276</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="F63" s="0" t="s">
+      <c r="F63" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3843,6 +3963,9 @@
       <c r="B64" s="3" t="s">
         <v>279</v>
       </c>
+      <c r="F64" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="65" customFormat="false" ht="36.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="3" t="s">
@@ -3851,16 +3974,19 @@
       <c r="B65" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="F65" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F65" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="3" t="s">
         <v>282</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>283</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3870,18 +3996,18 @@
       <c r="B67" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="F67" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F67" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="3" t="s">
         <v>286</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="F68" s="0" t="s">
+      <c r="F68" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3892,26 +4018,29 @@
       <c r="B69" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="F69" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F69" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="3" t="s">
         <v>290</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="71" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F70" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="3" t="s">
         <v>292</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="F71" s="0" t="s">
+      <c r="F71" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3922,18 +4051,18 @@
       <c r="B72" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="F72" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F72" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="3" t="s">
         <v>296</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="F73" s="0" t="s">
+      <c r="F73" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3944,6 +4073,9 @@
       <c r="B74" s="3" t="s">
         <v>299</v>
       </c>
+      <c r="F74" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="75" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="3" t="s">
@@ -3960,38 +4092,41 @@
       <c r="B76" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="F76" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F76" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="3" t="s">
         <v>304</v>
       </c>
       <c r="B77" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="F77" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F77" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="3" t="s">
         <v>306</v>
       </c>
       <c r="B78" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="F78" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F78" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="3" t="s">
         <v>308</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>309</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4001,7 +4136,7 @@
       <c r="B80" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="F80" s="0" t="s">
+      <c r="F80" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4012,7 +4147,7 @@
       <c r="B81" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="F81" s="0" t="s">
+      <c r="F81" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4023,7 +4158,7 @@
       <c r="B82" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="F82" s="0" t="s">
+      <c r="F82" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4034,7 +4169,7 @@
       <c r="B83" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="F83" s="0" t="s">
+      <c r="F83" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4045,7 +4180,7 @@
       <c r="B84" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="F84" s="0" t="s">
+      <c r="F84" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4056,34 +4191,10 @@
       <c r="B85" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="F85" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="F85" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -4100,11 +4211,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F100"/>
+  <dimension ref="A1:F78"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="145.76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="154.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="154.75"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4122,7 +4233,7 @@
       <c r="B2" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4133,7 +4244,7 @@
       <c r="B3" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="F3" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4145,14 +4256,14 @@
         <v>329</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
         <v>330</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="F5" s="0" t="s">
+      <c r="F5" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4163,7 +4274,7 @@
       <c r="B6" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="F6" s="0" t="s">
+      <c r="F6" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4174,18 +4285,18 @@
       <c r="B7" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="F7" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F7" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
         <v>336</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="F8" s="0" t="s">
+      <c r="F8" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4196,7 +4307,7 @@
       <c r="B9" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="F9" s="0" t="s">
+      <c r="F9" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4207,29 +4318,29 @@
       <c r="B10" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="F10" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F10" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
         <v>342</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="F11" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F11" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
         <v>344</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="F12" s="0" t="s">
+      <c r="F12" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4248,7 +4359,7 @@
       <c r="B14" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="F14" s="0" t="s">
+      <c r="F14" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4259,7 +4370,7 @@
       <c r="B15" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="F15" s="0" t="s">
+      <c r="F15" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4270,7 +4381,7 @@
       <c r="B16" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="F16" s="0" t="s">
+      <c r="F16" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4281,7 +4392,7 @@
       <c r="B17" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="F17" s="0" t="s">
+      <c r="F17" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4292,7 +4403,7 @@
       <c r="B18" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="F18" s="0" t="s">
+      <c r="F18" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4303,7 +4414,7 @@
       <c r="B19" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="F19" s="0" t="s">
+      <c r="F19" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4314,7 +4425,7 @@
       <c r="B20" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="F20" s="0" t="s">
+      <c r="F20" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4325,7 +4436,7 @@
       <c r="B21" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="F21" s="0" t="s">
+      <c r="F21" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4336,7 +4447,7 @@
       <c r="B22" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="F22" s="0" t="s">
+      <c r="F22" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4347,18 +4458,18 @@
       <c r="B23" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="F23" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F23" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
         <v>368</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>369</v>
       </c>
-      <c r="F24" s="0" t="s">
+      <c r="F24" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4369,7 +4480,7 @@
       <c r="B25" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="F25" s="0" t="s">
+      <c r="F25" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4380,18 +4491,18 @@
       <c r="B26" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="F26" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F26" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
         <v>374</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="F27" s="0" t="s">
+      <c r="F27" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4402,7 +4513,7 @@
       <c r="B28" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="F28" s="0" t="s">
+      <c r="F28" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4413,7 +4524,7 @@
       <c r="B29" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="F29" s="0" t="s">
+      <c r="F29" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4424,7 +4535,7 @@
       <c r="B30" s="3" t="s">
         <v>381</v>
       </c>
-      <c r="F30" s="0" t="s">
+      <c r="F30" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4435,7 +4546,7 @@
       <c r="B31" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="F31" s="0" t="s">
+      <c r="F31" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4446,7 +4557,7 @@
       <c r="B32" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="F32" s="0" t="s">
+      <c r="F32" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4457,7 +4568,7 @@
       <c r="B33" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="F33" s="0" t="s">
+      <c r="F33" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4469,25 +4580,25 @@
         <v>389</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
         <v>390</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="F35" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F35" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="33.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
         <v>392</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="F36" s="0" t="s">
+      <c r="F36" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4498,7 +4609,7 @@
       <c r="B37" s="3" t="s">
         <v>395</v>
       </c>
-      <c r="F37" s="0" t="s">
+      <c r="F37" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4509,7 +4620,7 @@
       <c r="B38" s="3" t="s">
         <v>397</v>
       </c>
-      <c r="F38" s="0" t="s">
+      <c r="F38" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4520,7 +4631,7 @@
       <c r="B39" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="F39" s="0" t="s">
+      <c r="F39" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4531,7 +4642,7 @@
       <c r="B40" s="3" t="s">
         <v>401</v>
       </c>
-      <c r="F40" s="0" t="s">
+      <c r="F40" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4542,7 +4653,7 @@
       <c r="B41" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="F41" s="0" t="s">
+      <c r="F41" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4553,7 +4664,7 @@
       <c r="B42" s="3" t="s">
         <v>405</v>
       </c>
-      <c r="F42" s="0" t="s">
+      <c r="F42" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4564,7 +4675,7 @@
       <c r="B43" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="F43" s="0" t="s">
+      <c r="F43" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4575,7 +4686,7 @@
       <c r="B44" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="F44" s="0" t="s">
+      <c r="F44" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4586,7 +4697,7 @@
       <c r="B45" s="3" t="s">
         <v>411</v>
       </c>
-      <c r="F45" s="0" t="s">
+      <c r="F45" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4597,7 +4708,7 @@
       <c r="B46" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="F46" s="0" t="s">
+      <c r="F46" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4608,7 +4719,7 @@
       <c r="B47" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="F47" s="0" t="s">
+      <c r="F47" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4619,7 +4730,7 @@
       <c r="B48" s="3" t="s">
         <v>417</v>
       </c>
-      <c r="F48" s="0" t="s">
+      <c r="F48" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4630,7 +4741,7 @@
       <c r="B49" s="3" t="s">
         <v>419</v>
       </c>
-      <c r="F49" s="0" t="s">
+      <c r="F49" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4641,7 +4752,7 @@
       <c r="B50" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="F50" s="0" t="s">
+      <c r="F50" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4652,7 +4763,7 @@
       <c r="B51" s="3" t="s">
         <v>423</v>
       </c>
-      <c r="F51" s="0" t="s">
+      <c r="F51" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4663,7 +4774,7 @@
       <c r="B52" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="F52" s="0" t="s">
+      <c r="F52" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4682,7 +4793,7 @@
       <c r="B54" s="3" t="s">
         <v>429</v>
       </c>
-      <c r="F54" s="0" t="s">
+      <c r="F54" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4693,29 +4804,29 @@
       <c r="B55" s="3" t="s">
         <v>431</v>
       </c>
-      <c r="F55" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F55" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
         <v>432</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>433</v>
       </c>
-      <c r="F56" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F56" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2" t="s">
         <v>434</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>435</v>
       </c>
-      <c r="F57" s="0" t="s">
+      <c r="F57" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4726,7 +4837,7 @@
       <c r="B58" s="3" t="s">
         <v>437</v>
       </c>
-      <c r="F58" s="0" t="s">
+      <c r="F58" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4737,7 +4848,7 @@
       <c r="B59" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="F59" s="0" t="s">
+      <c r="F59" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4748,7 +4859,7 @@
       <c r="B60" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="F60" s="0" t="s">
+      <c r="F60" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4760,14 +4871,14 @@
         <v>443</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2" t="s">
         <v>444</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>445</v>
       </c>
-      <c r="F62" s="0" t="s">
+      <c r="F62" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4778,29 +4889,29 @@
       <c r="B63" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="F63" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F63" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="2" t="s">
         <v>448</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="F64" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F64" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="2" t="s">
         <v>450</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>451</v>
       </c>
-      <c r="F65" s="0" t="s">
+      <c r="F65" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4811,7 +4922,7 @@
       <c r="B66" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="F66" s="0" t="s">
+      <c r="F66" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4822,7 +4933,7 @@
       <c r="B67" s="3" t="s">
         <v>455</v>
       </c>
-      <c r="F67" s="0" t="s">
+      <c r="F67" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4833,7 +4944,7 @@
       <c r="B68" s="3" t="s">
         <v>457</v>
       </c>
-      <c r="F68" s="0" t="s">
+      <c r="F68" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4844,7 +4955,7 @@
       <c r="B69" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="F69" s="0" t="s">
+      <c r="F69" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4863,7 +4974,7 @@
       <c r="B71" s="3" t="s">
         <v>463</v>
       </c>
-      <c r="F71" s="0" t="s">
+      <c r="F71" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4874,7 +4985,7 @@
       <c r="B72" s="3" t="s">
         <v>465</v>
       </c>
-      <c r="F72" s="0" t="s">
+      <c r="F72" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4885,7 +4996,7 @@
       <c r="B73" s="3" t="s">
         <v>467</v>
       </c>
-      <c r="F73" s="0" t="s">
+      <c r="F73" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4896,7 +5007,7 @@
       <c r="B74" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="F74" s="0" t="s">
+      <c r="F74" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4907,18 +5018,18 @@
       <c r="B75" s="3" t="s">
         <v>471</v>
       </c>
-      <c r="F75" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F75" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="2" t="s">
         <v>472</v>
       </c>
       <c r="B76" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="F76" s="0" t="s">
+      <c r="F76" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4929,7 +5040,7 @@
       <c r="B77" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="F77" s="0" t="s">
+      <c r="F77" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4940,75 +5051,9 @@
       <c r="B78" s="3" t="s">
         <v>477</v>
       </c>
-      <c r="F78" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="2"/>
-    </row>
-    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="2"/>
-    </row>
-    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="2"/>
-    </row>
-    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="2"/>
-    </row>
-    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="2"/>
-    </row>
-    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="2"/>
-    </row>
-    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="2"/>
-    </row>
-    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="2"/>
-    </row>
-    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="2"/>
-    </row>
-    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="2"/>
-    </row>
-    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="2"/>
-    </row>
-    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="2"/>
-    </row>
-    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="2"/>
-    </row>
-    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="2"/>
-    </row>
-    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="2"/>
-    </row>
-    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="2"/>
-    </row>
-    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="2"/>
-    </row>
-    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="2"/>
-    </row>
-    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="2"/>
-    </row>
-    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="2"/>
-    </row>
-    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="2"/>
-    </row>
-    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="2"/>
+      <c r="F78" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -5040,7 +5085,7 @@
       <c r="B1" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5051,13 +5096,13 @@
       <c r="B2" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2"/>
-      <c r="F3" s="0" t="s">
+      <c r="F3" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5068,7 +5113,7 @@
       <c r="B4" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="F4" s="0" t="s">
+      <c r="F4" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5079,13 +5124,13 @@
       <c r="B5" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="F5" s="0" t="s">
+      <c r="F5" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2"/>
-      <c r="F6" s="0" t="s">
+      <c r="F6" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5096,7 +5141,7 @@
       <c r="B7" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="F7" s="0" t="s">
+      <c r="F7" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5107,7 +5152,7 @@
       <c r="B8" s="2" t="s">
         <v>489</v>
       </c>
-      <c r="F8" s="0" t="s">
+      <c r="F8" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5118,7 +5163,7 @@
       <c r="B9" s="2" t="s">
         <v>491</v>
       </c>
-      <c r="F9" s="0" t="s">
+      <c r="F9" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5129,7 +5174,7 @@
       <c r="B10" s="2" t="s">
         <v>493</v>
       </c>
-      <c r="F10" s="0" t="s">
+      <c r="F10" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5140,24 +5185,24 @@
       <c r="B11" s="2" t="s">
         <v>495</v>
       </c>
-      <c r="F11" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="57.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F11" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
         <v>496</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="F12" s="0" t="s">
+      <c r="F12" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2"/>
-      <c r="F13" s="0" t="s">
+      <c r="F13" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5168,24 +5213,24 @@
       <c r="B14" s="2" t="s">
         <v>499</v>
       </c>
-      <c r="F14" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="45.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F14" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
         <v>500</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="F15" s="0" t="s">
+      <c r="F15" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2"/>
-      <c r="F16" s="0" t="s">
+      <c r="F16" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5196,7 +5241,7 @@
       <c r="B17" s="2" t="s">
         <v>503</v>
       </c>
-      <c r="F17" s="0" t="s">
+      <c r="F17" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5207,13 +5252,13 @@
       <c r="B18" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="F18" s="0" t="s">
+      <c r="F18" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2"/>
-      <c r="F19" s="0" t="s">
+      <c r="F19" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5224,7 +5269,7 @@
       <c r="B20" s="2" t="s">
         <v>507</v>
       </c>
-      <c r="F20" s="0" t="s">
+      <c r="F20" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5235,7 +5280,7 @@
       <c r="B21" s="2" t="s">
         <v>509</v>
       </c>
-      <c r="F21" s="0" t="s">
+      <c r="F21" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5246,7 +5291,7 @@
       <c r="B22" s="2" t="s">
         <v>511</v>
       </c>
-      <c r="F22" s="0" t="s">
+      <c r="F22" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5257,7 +5302,7 @@
       <c r="B23" s="2" t="s">
         <v>513</v>
       </c>
-      <c r="F23" s="0" t="s">
+      <c r="F23" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5268,7 +5313,7 @@
       <c r="B24" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="F24" s="0" t="s">
+      <c r="F24" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5279,18 +5324,18 @@
       <c r="B25" s="2" t="s">
         <v>517</v>
       </c>
-      <c r="F25" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F25" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
         <v>518</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>519</v>
       </c>
-      <c r="F26" s="0" t="s">
+      <c r="F26" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5301,7 +5346,7 @@
       <c r="B27" s="2" t="s">
         <v>521</v>
       </c>
-      <c r="F27" s="0" t="s">
+      <c r="F27" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5312,13 +5357,13 @@
       <c r="B28" s="2" t="s">
         <v>523</v>
       </c>
-      <c r="F28" s="0" t="s">
+      <c r="F28" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2"/>
-      <c r="F29" s="0" t="s">
+      <c r="F29" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5329,7 +5374,7 @@
       <c r="B30" s="2" t="s">
         <v>525</v>
       </c>
-      <c r="F30" s="0" t="s">
+      <c r="F30" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5340,13 +5385,13 @@
       <c r="B31" s="2" t="s">
         <v>527</v>
       </c>
-      <c r="F31" s="0" t="s">
+      <c r="F31" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2"/>
-      <c r="F32" s="0" t="s">
+      <c r="F32" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5357,7 +5402,7 @@
       <c r="B33" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="F33" s="0" t="s">
+      <c r="F33" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5368,13 +5413,13 @@
       <c r="B34" s="2" t="s">
         <v>531</v>
       </c>
-      <c r="F34" s="0" t="s">
+      <c r="F34" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2"/>
-      <c r="F35" s="0" t="s">
+      <c r="F35" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5385,24 +5430,24 @@
       <c r="B36" s="2" t="s">
         <v>533</v>
       </c>
-      <c r="F36" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F36" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
         <v>534</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="F37" s="0" t="s">
+      <c r="F37" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2"/>
-      <c r="F38" s="0" t="s">
+      <c r="F38" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5413,7 +5458,7 @@
       <c r="B39" s="2" t="s">
         <v>537</v>
       </c>
-      <c r="F39" s="0" t="s">
+      <c r="F39" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5424,13 +5469,13 @@
       <c r="B40" s="2" t="s">
         <v>539</v>
       </c>
-      <c r="F40" s="0" t="s">
+      <c r="F40" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2"/>
-      <c r="F41" s="0" t="s">
+      <c r="F41" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5441,7 +5486,7 @@
       <c r="B42" s="2" t="s">
         <v>541</v>
       </c>
-      <c r="F42" s="0" t="s">
+      <c r="F42" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5452,7 +5497,7 @@
       <c r="B43" s="2" t="s">
         <v>543</v>
       </c>
-      <c r="F43" s="0" t="s">
+      <c r="F43" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5463,7 +5508,7 @@
       <c r="B44" s="2" t="s">
         <v>545</v>
       </c>
-      <c r="F44" s="0" t="s">
+      <c r="F44" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5474,7 +5519,7 @@
       <c r="B45" s="2" t="s">
         <v>547</v>
       </c>
-      <c r="F45" s="0" t="s">
+      <c r="F45" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5485,7 +5530,7 @@
       <c r="B46" s="2" t="s">
         <v>549</v>
       </c>
-      <c r="F46" s="0" t="s">
+      <c r="F46" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5496,24 +5541,24 @@
       <c r="B47" s="2" t="s">
         <v>551</v>
       </c>
-      <c r="F47" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="34.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F47" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
         <v>552</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>553</v>
       </c>
-      <c r="F48" s="0" t="s">
+      <c r="F48" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2"/>
-      <c r="F49" s="0" t="s">
+      <c r="F49" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5524,7 +5569,7 @@
       <c r="B50" s="2" t="s">
         <v>555</v>
       </c>
-      <c r="F50" s="0" t="s">
+      <c r="F50" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5535,13 +5580,13 @@
       <c r="B51" s="2" t="s">
         <v>557</v>
       </c>
-      <c r="F51" s="0" t="s">
+      <c r="F51" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2"/>
-      <c r="F52" s="0" t="s">
+      <c r="F52" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5552,7 +5597,7 @@
       <c r="B53" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="F53" s="0" t="s">
+      <c r="F53" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5563,13 +5608,13 @@
       <c r="B54" s="2" t="s">
         <v>561</v>
       </c>
-      <c r="F54" s="0" t="s">
+      <c r="F54" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2"/>
-      <c r="F55" s="0" t="s">
+      <c r="F55" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5580,7 +5625,7 @@
       <c r="B56" s="2" t="s">
         <v>563</v>
       </c>
-      <c r="F56" s="0" t="s">
+      <c r="F56" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5591,13 +5636,13 @@
       <c r="B57" s="2" t="s">
         <v>565</v>
       </c>
-      <c r="F57" s="0" t="s">
+      <c r="F57" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2"/>
-      <c r="F58" s="0" t="s">
+      <c r="F58" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5608,18 +5653,18 @@
       <c r="B59" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="F59" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F59" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="2" t="s">
         <v>568</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>569</v>
       </c>
-      <c r="F60" s="0" t="s">
+      <c r="F60" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5630,7 +5675,7 @@
       <c r="B61" s="2" t="s">
         <v>571</v>
       </c>
-      <c r="F61" s="0" t="s">
+      <c r="F61" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5641,24 +5686,24 @@
       <c r="B62" s="2" t="s">
         <v>573</v>
       </c>
-      <c r="F62" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="45.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F62" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2" t="s">
         <v>574</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>575</v>
       </c>
-      <c r="F63" s="0" t="s">
+      <c r="F63" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="2"/>
-      <c r="F64" s="0" t="s">
+      <c r="F64" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5669,7 +5714,7 @@
       <c r="B65" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="F65" s="0" t="s">
+      <c r="F65" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5680,13 +5725,13 @@
       <c r="B66" s="2" t="s">
         <v>579</v>
       </c>
-      <c r="F66" s="0" t="s">
+      <c r="F66" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="2"/>
-      <c r="F67" s="0" t="s">
+      <c r="F67" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5697,24 +5742,24 @@
       <c r="B68" s="2" t="s">
         <v>581</v>
       </c>
-      <c r="F68" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="45.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F68" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="2" t="s">
         <v>582</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>583</v>
       </c>
-      <c r="F69" s="0" t="s">
+      <c r="F69" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="2"/>
-      <c r="F70" s="0" t="s">
+      <c r="F70" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5725,7 +5770,7 @@
       <c r="B71" s="2" t="s">
         <v>585</v>
       </c>
-      <c r="F71" s="0" t="s">
+      <c r="F71" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5736,12 +5781,12 @@
       <c r="B72" s="2" t="s">
         <v>587</v>
       </c>
-      <c r="F72" s="0" t="s">
+      <c r="F72" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F73" s="0" t="s">
+      <c r="F73" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5752,13 +5797,13 @@
       <c r="B74" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="F74" s="0" t="s">
+      <c r="F74" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="2"/>
-      <c r="F75" s="0" t="s">
+      <c r="F75" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5769,13 +5814,13 @@
       <c r="B76" s="2" t="s">
         <v>591</v>
       </c>
-      <c r="F76" s="0" t="s">
+      <c r="F76" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="2"/>
-      <c r="F77" s="0" t="s">
+      <c r="F77" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5786,13 +5831,13 @@
       <c r="B78" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="F78" s="0" t="s">
+      <c r="F78" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="2"/>
-      <c r="F79" s="0" t="s">
+      <c r="F79" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5803,13 +5848,13 @@
       <c r="B80" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="F80" s="0" t="s">
+      <c r="F80" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="2"/>
-      <c r="F81" s="0" t="s">
+      <c r="F81" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5820,30 +5865,30 @@
       <c r="B82" s="2" t="s">
         <v>597</v>
       </c>
-      <c r="F82" s="0" t="s">
+      <c r="F82" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="2"/>
-      <c r="F83" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="57.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F83" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="2" t="s">
         <v>598</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>599</v>
       </c>
-      <c r="F84" s="0" t="s">
+      <c r="F84" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="2"/>
-      <c r="F85" s="0" t="s">
+      <c r="F85" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5854,13 +5899,13 @@
       <c r="B86" s="2" t="s">
         <v>601</v>
       </c>
-      <c r="F86" s="0" t="s">
+      <c r="F86" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="2"/>
-      <c r="F87" s="0" t="s">
+      <c r="F87" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5872,7 +5917,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="45.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="2" t="s">
         <v>604</v>
       </c>
@@ -5880,7 +5925,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="45.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="2" t="s">
         <v>606</v>
       </c>
@@ -5888,7 +5933,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="45.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="2" t="s">
         <v>608</v>
       </c>
@@ -5896,7 +5941,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="57.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="2" t="s">
         <v>610</v>
       </c>
@@ -5904,18 +5949,18 @@
         <v>611</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="57.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="2" t="s">
         <v>612</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="F93" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="94" customFormat="false" ht="45.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F93" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="2" t="s">
         <v>614</v>
       </c>
@@ -5923,7 +5968,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="45.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="2" t="s">
         <v>616</v>
       </c>
@@ -5931,7 +5976,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="45.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="2" t="s">
         <v>618</v>
       </c>
@@ -5939,7 +5984,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="45.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="2" t="s">
         <v>620</v>
       </c>
@@ -5947,7 +5992,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="45.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="2" t="s">
         <v>622</v>
       </c>
@@ -5955,7 +6000,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="57.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="2" t="s">
         <v>624</v>
       </c>
@@ -5963,7 +6008,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="45.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="2" t="s">
         <v>626</v>
       </c>
@@ -5986,11 +6031,11 @@
       <c r="B102" s="2" t="s">
         <v>631</v>
       </c>
-      <c r="F102" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="103" customFormat="false" ht="34.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F102" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="2" t="s">
         <v>632</v>
       </c>
@@ -5998,25 +6043,25 @@
         <v>633</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="2" t="s">
         <v>634</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>635</v>
       </c>
-      <c r="F104" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="105" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F104" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="2" t="s">
         <v>636</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>637</v>
       </c>
-      <c r="F105" s="0" t="s">
+      <c r="F105" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -6027,7 +6072,7 @@
       <c r="B106" s="2" t="s">
         <v>639</v>
       </c>
-      <c r="F106" s="0" t="s">
+      <c r="F106" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -6038,18 +6083,18 @@
       <c r="B107" s="2" t="s">
         <v>641</v>
       </c>
-      <c r="F107" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="108" customFormat="false" ht="34.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F107" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="2" t="s">
         <v>642</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>643</v>
       </c>
-      <c r="F108" s="0" t="s">
+      <c r="F108" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -6060,7 +6105,7 @@
       <c r="B109" s="2" t="s">
         <v>645</v>
       </c>
-      <c r="F109" s="0" t="s">
+      <c r="F109" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -6071,7 +6116,7 @@
       <c r="B110" s="2" t="s">
         <v>647</v>
       </c>
-      <c r="F110" s="0" t="s">
+      <c r="F110" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -6083,14 +6128,14 @@
         <v>649</v>
       </c>
     </row>
-    <row r="112" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="2" t="s">
         <v>650</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>651</v>
       </c>
-      <c r="F112" s="0" t="s">
+      <c r="F112" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -6101,18 +6146,18 @@
       <c r="B113" s="2" t="s">
         <v>653</v>
       </c>
-      <c r="F113" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="114" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F113" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="2" t="s">
         <v>654</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>655</v>
       </c>
-      <c r="F114" s="0" t="s">
+      <c r="F114" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -6123,7 +6168,7 @@
       <c r="B115" s="2" t="s">
         <v>657</v>
       </c>
-      <c r="F115" s="0" t="s">
+      <c r="F115" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -6134,7 +6179,7 @@
       <c r="B116" s="2" t="s">
         <v>659</v>
       </c>
-      <c r="F116" s="0" t="s">
+      <c r="F116" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -6146,25 +6191,25 @@
         <v>661</v>
       </c>
     </row>
-    <row r="118" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="2" t="s">
         <v>662</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>663</v>
       </c>
-      <c r="F118" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="119" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F118" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="2" t="s">
         <v>664</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>665</v>
       </c>
-      <c r="F119" s="0" t="s">
+      <c r="F119" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -6175,18 +6220,18 @@
       <c r="B120" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="F120" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="121" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F120" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="2" t="s">
         <v>668</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>669</v>
       </c>
-      <c r="F121" s="0" t="s">
+      <c r="F121" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -6205,7 +6250,7 @@
       <c r="B123" s="2" t="s">
         <v>673</v>
       </c>
-      <c r="F123" s="0" t="s">
+      <c r="F123" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -6216,7 +6261,7 @@
       <c r="B124" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="F124" s="0" t="s">
+      <c r="F124" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -6227,18 +6272,18 @@
       <c r="B125" s="2" t="s">
         <v>677</v>
       </c>
-      <c r="F125" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="126" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F125" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="2" t="s">
         <v>678</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>679</v>
       </c>
-      <c r="F126" s="0" t="s">
+      <c r="F126" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -6250,14 +6295,14 @@
         <v>681</v>
       </c>
     </row>
-    <row r="128" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="2" t="s">
         <v>682</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>683</v>
       </c>
-      <c r="F128" s="0" t="s">
+      <c r="F128" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -6268,18 +6313,18 @@
       <c r="B129" s="2" t="s">
         <v>685</v>
       </c>
-      <c r="F129" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="130" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F129" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="2" t="s">
         <v>686</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>687</v>
       </c>
-      <c r="F130" s="0" t="s">
+      <c r="F130" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -6291,25 +6336,25 @@
         <v>689</v>
       </c>
     </row>
-    <row r="132" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="2" t="s">
         <v>690</v>
       </c>
       <c r="B132" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="F132" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="133" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F132" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="2" t="s">
         <v>692</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>693</v>
       </c>
-      <c r="F133" s="0" t="s">
+      <c r="F133" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -6320,7 +6365,7 @@
       <c r="B134" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="F134" s="0" t="s">
+      <c r="F134" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -6331,7 +6376,7 @@
       <c r="B135" s="2" t="s">
         <v>697</v>
       </c>
-      <c r="F135" s="0" t="s">
+      <c r="F135" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -6343,25 +6388,25 @@
         <v>699</v>
       </c>
     </row>
-    <row r="137" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="2" t="s">
         <v>700</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="F137" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="138" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F137" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="2" t="s">
         <v>702</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>703</v>
       </c>
-      <c r="F138" s="0" t="s">
+      <c r="F138" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -6372,7 +6417,7 @@
       <c r="B139" s="2" t="s">
         <v>705</v>
       </c>
-      <c r="F139" s="0" t="s">
+      <c r="F139" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -6383,7 +6428,7 @@
       <c r="B140" s="2" t="s">
         <v>707</v>
       </c>
-      <c r="F140" s="0" t="s">
+      <c r="F140" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -6395,25 +6440,25 @@
         <v>709</v>
       </c>
     </row>
-    <row r="142" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="2" t="s">
         <v>710</v>
       </c>
       <c r="B142" s="2" t="s">
         <v>711</v>
       </c>
-      <c r="F142" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="143" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F142" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="143" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="2" t="s">
         <v>712</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>713</v>
       </c>
-      <c r="F143" s="0" t="s">
+      <c r="F143" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -6424,7 +6469,7 @@
       <c r="B144" s="2" t="s">
         <v>715</v>
       </c>
-      <c r="F144" s="0" t="s">
+      <c r="F144" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -6435,7 +6480,7 @@
       <c r="B145" s="2" t="s">
         <v>717</v>
       </c>
-      <c r="F145" s="0" t="s">
+      <c r="F145" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -6447,25 +6492,25 @@
         <v>719</v>
       </c>
     </row>
-    <row r="147" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="147" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="2" t="s">
         <v>720</v>
       </c>
       <c r="B147" s="2" t="s">
         <v>721</v>
       </c>
-      <c r="F147" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="148" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F147" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="2" t="s">
         <v>722</v>
       </c>
       <c r="B148" s="2" t="s">
         <v>723</v>
       </c>
-      <c r="F148" s="0" t="s">
+      <c r="F148" s="1" t="s">
         <v>4</v>
       </c>
     </row>

--- a/src/main/resources/espacios/Software/0 - arquitectura hexagonal.xlsx
+++ b/src/main/resources/espacios/Software/0 - arquitectura hexagonal.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Arquitectura Hexagonal" sheetId="1" state="visible" r:id="rId3"/>
@@ -2204,7 +2204,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -2225,6 +2225,13 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2274,15 +2281,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2414,22 +2421,23 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="115.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="130.56"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="3" style="2" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" customFormat="false" ht="45.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="2" customFormat="false" ht="49.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>3</v>
       </c>
       <c r="F2" s="1" t="s">
@@ -2437,10 +2445,10 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>6</v>
       </c>
       <c r="F3" s="1" t="s">
@@ -2448,10 +2456,10 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="34.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F4" s="1" t="s">
@@ -2459,10 +2467,10 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F5" s="1" t="s">
@@ -2470,10 +2478,10 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F6" s="1" t="s">
@@ -2481,10 +2489,10 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>14</v>
       </c>
       <c r="F7" s="1" t="s">
@@ -2492,10 +2500,10 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>16</v>
       </c>
       <c r="F8" s="1" t="s">
@@ -2503,10 +2511,10 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="1" t="s">
@@ -2514,10 +2522,10 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>20</v>
       </c>
       <c r="F10" s="1" t="s">
@@ -2525,10 +2533,10 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>22</v>
       </c>
       <c r="F11" s="1" t="s">
@@ -2536,10 +2544,10 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F12" s="1" t="s">
@@ -2547,10 +2555,10 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F13" s="1" t="s">
@@ -2558,10 +2566,10 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F14" s="1" t="s">
@@ -2569,32 +2577,32 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="3" t="s">
         <v>30</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
+    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="3" t="s">
         <v>32</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
+    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="3" t="s">
         <v>34</v>
       </c>
       <c r="F17" s="1" t="s">
@@ -2602,21 +2610,21 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="45.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="s">
+    <row r="19" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F19" s="1" t="s">
@@ -2624,10 +2632,10 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="3" t="s">
         <v>40</v>
       </c>
       <c r="F20" s="1" t="s">
@@ -2635,10 +2643,10 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="34.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F21" s="1" t="s">
@@ -2646,32 +2654,32 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="3" t="s">
         <v>44</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2" t="s">
+    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="3" t="s">
         <v>46</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2" t="s">
+    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="3" t="s">
         <v>48</v>
       </c>
       <c r="F24" s="1" t="s">
@@ -2679,10 +2687,10 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="3" t="s">
         <v>50</v>
       </c>
       <c r="F25" s="1" t="s">
@@ -2690,10 +2698,10 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="34.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="3" t="s">
         <v>52</v>
       </c>
       <c r="F26" s="1" t="s">
@@ -2701,10 +2709,10 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="3" t="s">
         <v>54</v>
       </c>
       <c r="F27" s="1" t="s">
@@ -2712,10 +2720,10 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="3" t="s">
         <v>56</v>
       </c>
       <c r="F28" s="1" t="s">
@@ -2723,21 +2731,21 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="3" t="s">
         <v>58</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="2" t="s">
+    <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="3" t="s">
         <v>60</v>
       </c>
       <c r="F30" s="1" t="s">
@@ -2745,10 +2753,10 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="3" t="s">
         <v>62</v>
       </c>
       <c r="F31" s="1" t="s">
@@ -2756,10 +2764,10 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="2" t="s">
+      <c r="A32" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F32" s="1" t="s">
@@ -2767,10 +2775,10 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="2" t="s">
+      <c r="A33" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="3" t="s">
         <v>66</v>
       </c>
       <c r="F33" s="1" t="s">
@@ -2778,10 +2786,10 @@
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="2" t="s">
+      <c r="A34" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="3" t="s">
         <v>68</v>
       </c>
       <c r="F34" s="1" t="s">
@@ -2789,10 +2797,10 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="2" t="s">
+      <c r="A35" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="3" t="s">
         <v>70</v>
       </c>
       <c r="F35" s="1" t="s">
@@ -2800,10 +2808,10 @@
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="2" t="s">
+      <c r="A36" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="3" t="s">
         <v>72</v>
       </c>
       <c r="F36" s="1" t="s">
@@ -2811,21 +2819,21 @@
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="2" t="s">
+      <c r="A37" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B37" s="3" t="s">
         <v>74</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="34.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="2" t="s">
+    <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B38" s="3" t="s">
         <v>76</v>
       </c>
       <c r="F38" s="1" t="s">
@@ -2833,19 +2841,19 @@
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="2" t="s">
+      <c r="A39" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" s="3" t="s">
         <v>78</v>
       </c>
       <c r="F39" s="1"/>
     </row>
-    <row r="40" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="2" t="s">
+    <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B40" s="3" t="s">
         <v>80</v>
       </c>
       <c r="F40" s="1" t="s">
@@ -2853,21 +2861,21 @@
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="2" t="s">
+      <c r="A41" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="B41" s="3" t="s">
         <v>82</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="2" t="s">
+    <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B42" s="3" t="s">
         <v>84</v>
       </c>
       <c r="F42" s="1" t="s">
@@ -2875,10 +2883,10 @@
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="2" t="s">
+      <c r="A43" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="B43" s="3" t="s">
         <v>86</v>
       </c>
       <c r="F43" s="1" t="s">
@@ -2886,10 +2894,10 @@
       </c>
     </row>
     <row r="44" customFormat="false" ht="34.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="2" t="s">
+      <c r="A44" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="B44" s="3" t="s">
         <v>88</v>
       </c>
       <c r="F44" s="1" t="s">
@@ -2897,10 +2905,10 @@
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="2" t="s">
+      <c r="A45" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B45" s="3" t="s">
         <v>90</v>
       </c>
       <c r="F45" s="1" t="s">
@@ -2908,10 +2916,10 @@
       </c>
     </row>
     <row r="46" customFormat="false" ht="34.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="2" t="s">
+      <c r="A46" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B46" s="3" t="s">
         <v>92</v>
       </c>
       <c r="F46" s="1" t="s">
@@ -2919,21 +2927,21 @@
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="2" t="s">
+      <c r="A47" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B47" s="3" t="s">
         <v>94</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="2" t="s">
+    <row r="48" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B48" s="3" t="s">
         <v>96</v>
       </c>
       <c r="F48" s="1" t="s">
@@ -2941,21 +2949,21 @@
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="2" t="s">
+      <c r="A49" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="B49" s="3" t="s">
         <v>98</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="2" t="s">
+    <row r="50" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="B50" s="3" t="s">
         <v>100</v>
       </c>
       <c r="F50" s="1" t="s">
@@ -2963,21 +2971,21 @@
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="2" t="s">
+      <c r="A51" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="B51" s="3" t="s">
         <v>102</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="2" t="s">
+    <row r="52" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="B52" s="3" t="s">
         <v>104</v>
       </c>
       <c r="F52" s="1" t="s">
@@ -2985,21 +2993,21 @@
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="2" t="s">
+      <c r="A53" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="B53" s="3" t="s">
         <v>106</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="2" t="s">
+    <row r="54" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="B54" s="3" t="s">
         <v>108</v>
       </c>
       <c r="F54" s="1" t="s">
@@ -3007,21 +3015,21 @@
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="2" t="s">
+      <c r="A55" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="B55" s="3" t="s">
         <v>110</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="2" t="s">
+    <row r="56" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="B56" s="3" t="s">
         <v>112</v>
       </c>
       <c r="F56" s="1" t="s">
@@ -3029,21 +3037,21 @@
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="2" t="s">
+      <c r="A57" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="B57" s="2" t="s">
+      <c r="B57" s="3" t="s">
         <v>114</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="34.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="2" t="s">
+    <row r="58" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="B58" s="3" t="s">
         <v>116</v>
       </c>
       <c r="F58" s="1" t="s">
@@ -3051,21 +3059,21 @@
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="2" t="s">
+      <c r="A59" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="B59" s="3" t="s">
         <v>118</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="2" t="s">
+    <row r="60" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="B60" s="3" t="s">
         <v>120</v>
       </c>
       <c r="F60" s="1" t="s">
@@ -3073,21 +3081,21 @@
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="2" t="s">
+      <c r="A61" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="B61" s="2" t="s">
+      <c r="B61" s="3" t="s">
         <v>122</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="2" t="s">
+    <row r="62" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="B62" s="2" t="s">
+      <c r="B62" s="3" t="s">
         <v>124</v>
       </c>
       <c r="F62" s="1" t="s">
@@ -3095,21 +3103,21 @@
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="2" t="s">
+      <c r="A63" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="B63" s="2" t="s">
+      <c r="B63" s="3" t="s">
         <v>126</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="2" t="s">
+    <row r="64" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="B64" s="2" t="s">
+      <c r="B64" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F64" s="1" t="s">
@@ -3117,19 +3125,19 @@
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="2" t="s">
+      <c r="A65" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="B65" s="2" t="s">
+      <c r="B65" s="3" t="s">
         <v>130</v>
       </c>
       <c r="F65" s="1"/>
     </row>
-    <row r="66" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="2" t="s">
+    <row r="66" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="B66" s="2" t="s">
+      <c r="B66" s="3" t="s">
         <v>132</v>
       </c>
       <c r="F66" s="1" t="s">
@@ -3137,21 +3145,21 @@
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="2" t="s">
+      <c r="A67" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="B67" s="2" t="s">
+      <c r="B67" s="3" t="s">
         <v>134</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="2" t="s">
+    <row r="68" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="B68" s="2" t="s">
+      <c r="B68" s="3" t="s">
         <v>136</v>
       </c>
       <c r="F68" s="1" t="s">
@@ -3159,10 +3167,10 @@
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="2" t="s">
+      <c r="A69" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="B69" s="2" t="s">
+      <c r="B69" s="3" t="s">
         <v>138</v>
       </c>
       <c r="F69" s="1" t="s">
@@ -3170,10 +3178,10 @@
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="2" t="s">
+      <c r="A70" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="B70" s="2" t="s">
+      <c r="B70" s="3" t="s">
         <v>140</v>
       </c>
       <c r="F70" s="1" t="s">
@@ -3181,10 +3189,10 @@
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="2" t="s">
+      <c r="A71" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="B71" s="2" t="s">
+      <c r="B71" s="3" t="s">
         <v>142</v>
       </c>
       <c r="F71" s="1" t="s">
@@ -3192,10 +3200,10 @@
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="2" t="s">
+      <c r="A72" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="B72" s="2" t="s">
+      <c r="B72" s="3" t="s">
         <v>144</v>
       </c>
       <c r="F72" s="1" t="s">
@@ -3203,21 +3211,21 @@
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="2" t="s">
+      <c r="A73" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="B73" s="2" t="s">
+      <c r="B73" s="3" t="s">
         <v>146</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="2" t="s">
+    <row r="74" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="B74" s="2" t="s">
+      <c r="B74" s="3" t="s">
         <v>148</v>
       </c>
       <c r="F74" s="1" t="s">
@@ -3225,21 +3233,21 @@
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="2" t="s">
+      <c r="A75" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="B75" s="2" t="s">
+      <c r="B75" s="3" t="s">
         <v>150</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="2" t="s">
+    <row r="76" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="B76" s="2" t="s">
+      <c r="B76" s="3" t="s">
         <v>152</v>
       </c>
       <c r="F76" s="1" t="s">
@@ -3267,6 +3275,7 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="147.47"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="185.36"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="3" style="2" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3332,7 +3341,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
         <v>165</v>
       </c>
@@ -3442,7 +3451,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="45.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
         <v>185</v>
       </c>
@@ -3453,7 +3462,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="34.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
         <v>187</v>
       </c>
@@ -3530,7 +3539,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
         <v>201</v>
       </c>
@@ -3596,7 +3605,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="45.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
         <v>213</v>
       </c>
@@ -3607,7 +3616,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="57.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
         <v>215</v>
       </c>
@@ -3791,7 +3800,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="3" t="s">
         <v>248</v>
       </c>
@@ -3879,7 +3888,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="3" t="s">
         <v>264</v>
       </c>
@@ -3923,7 +3932,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="3" t="s">
         <v>272</v>
       </c>
@@ -3978,7 +3987,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="3" t="s">
         <v>282</v>
       </c>
@@ -4022,7 +4031,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="3" t="s">
         <v>290</v>
       </c>
@@ -4118,7 +4127,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="22.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="3" t="s">
         <v>308</v>
       </c>
@@ -4216,10 +4225,11 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="145.76"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="154.75"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="3" style="2" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>322</v>
       </c>
       <c r="B1" s="3" t="s">
@@ -4227,7 +4237,7 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>324</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -4238,7 +4248,7 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>326</v>
       </c>
       <c r="B3" s="3" t="s">
@@ -4249,7 +4259,7 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>328</v>
       </c>
       <c r="B4" s="3" t="s">
@@ -4257,7 +4267,7 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="3" t="s">
         <v>330</v>
       </c>
       <c r="B5" s="3" t="s">
@@ -4268,7 +4278,7 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="3" t="s">
         <v>332</v>
       </c>
       <c r="B6" s="3" t="s">
@@ -4279,7 +4289,7 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="3" t="s">
         <v>334</v>
       </c>
       <c r="B7" s="3" t="s">
@@ -4290,7 +4300,7 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="3" t="s">
         <v>336</v>
       </c>
       <c r="B8" s="3" t="s">
@@ -4301,7 +4311,7 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="3" t="s">
         <v>338</v>
       </c>
       <c r="B9" s="3" t="s">
@@ -4312,7 +4322,7 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="3" t="s">
         <v>340</v>
       </c>
       <c r="B10" s="3" t="s">
@@ -4323,7 +4333,7 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="3" t="s">
         <v>342</v>
       </c>
       <c r="B11" s="3" t="s">
@@ -4334,7 +4344,7 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="3" t="s">
         <v>344</v>
       </c>
       <c r="B12" s="3" t="s">
@@ -4345,7 +4355,7 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="3" t="s">
         <v>346</v>
       </c>
       <c r="B13" s="3" t="s">
@@ -4353,7 +4363,7 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="3" t="s">
         <v>348</v>
       </c>
       <c r="B14" s="3" t="s">
@@ -4364,7 +4374,7 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="3" t="s">
         <v>350</v>
       </c>
       <c r="B15" s="3" t="s">
@@ -4375,7 +4385,7 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="3" t="s">
         <v>352</v>
       </c>
       <c r="B16" s="3" t="s">
@@ -4386,7 +4396,7 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="3" t="s">
         <v>354</v>
       </c>
       <c r="B17" s="3" t="s">
@@ -4397,7 +4407,7 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="3" t="s">
         <v>356</v>
       </c>
       <c r="B18" s="3" t="s">
@@ -4408,7 +4418,7 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="3" t="s">
         <v>358</v>
       </c>
       <c r="B19" s="3" t="s">
@@ -4419,7 +4429,7 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="3" t="s">
         <v>360</v>
       </c>
       <c r="B20" s="3" t="s">
@@ -4430,7 +4440,7 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="3" t="s">
         <v>362</v>
       </c>
       <c r="B21" s="3" t="s">
@@ -4441,7 +4451,7 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="3" t="s">
         <v>364</v>
       </c>
       <c r="B22" s="3" t="s">
@@ -4452,7 +4462,7 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="3" t="s">
         <v>366</v>
       </c>
       <c r="B23" s="3" t="s">
@@ -4463,7 +4473,7 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="3" t="s">
         <v>368</v>
       </c>
       <c r="B24" s="3" t="s">
@@ -4474,7 +4484,7 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="3" t="s">
         <v>370</v>
       </c>
       <c r="B25" s="3" t="s">
@@ -4485,7 +4495,7 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="3" t="s">
         <v>372</v>
       </c>
       <c r="B26" s="3" t="s">
@@ -4496,7 +4506,7 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="3" t="s">
         <v>374</v>
       </c>
       <c r="B27" s="3" t="s">
@@ -4507,7 +4517,7 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="3" t="s">
         <v>376</v>
       </c>
       <c r="B28" s="3" t="s">
@@ -4518,7 +4528,7 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="3" t="s">
         <v>378</v>
       </c>
       <c r="B29" s="3" t="s">
@@ -4529,7 +4539,7 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="3" t="s">
         <v>380</v>
       </c>
       <c r="B30" s="3" t="s">
@@ -4540,7 +4550,7 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="3" t="s">
         <v>382</v>
       </c>
       <c r="B31" s="3" t="s">
@@ -4551,7 +4561,7 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="2" t="s">
+      <c r="A32" s="3" t="s">
         <v>384</v>
       </c>
       <c r="B32" s="3" t="s">
@@ -4562,7 +4572,7 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="2" t="s">
+      <c r="A33" s="3" t="s">
         <v>386</v>
       </c>
       <c r="B33" s="3" t="s">
@@ -4573,7 +4583,7 @@
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="2" t="s">
+      <c r="A34" s="3" t="s">
         <v>388</v>
       </c>
       <c r="B34" s="3" t="s">
@@ -4581,7 +4591,7 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="2" t="s">
+      <c r="A35" s="3" t="s">
         <v>390</v>
       </c>
       <c r="B35" s="3" t="s">
@@ -4592,7 +4602,7 @@
       </c>
     </row>
     <row r="36" customFormat="false" ht="33.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="2" t="s">
+      <c r="A36" s="3" t="s">
         <v>392</v>
       </c>
       <c r="B36" s="3" t="s">
@@ -4603,7 +4613,7 @@
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="2" t="s">
+      <c r="A37" s="3" t="s">
         <v>394</v>
       </c>
       <c r="B37" s="3" t="s">
@@ -4614,7 +4624,7 @@
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="2" t="s">
+      <c r="A38" s="3" t="s">
         <v>396</v>
       </c>
       <c r="B38" s="3" t="s">
@@ -4625,7 +4635,7 @@
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="2" t="s">
+      <c r="A39" s="3" t="s">
         <v>398</v>
       </c>
       <c r="B39" s="3" t="s">
@@ -4636,7 +4646,7 @@
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="2" t="s">
+      <c r="A40" s="3" t="s">
         <v>400</v>
       </c>
       <c r="B40" s="3" t="s">
@@ -4647,7 +4657,7 @@
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="2" t="s">
+      <c r="A41" s="3" t="s">
         <v>402</v>
       </c>
       <c r="B41" s="3" t="s">
@@ -4658,7 +4668,7 @@
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="2" t="s">
+      <c r="A42" s="3" t="s">
         <v>404</v>
       </c>
       <c r="B42" s="3" t="s">
@@ -4669,7 +4679,7 @@
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="2" t="s">
+      <c r="A43" s="3" t="s">
         <v>406</v>
       </c>
       <c r="B43" s="3" t="s">
@@ -4680,7 +4690,7 @@
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="2" t="s">
+      <c r="A44" s="3" t="s">
         <v>408</v>
       </c>
       <c r="B44" s="3" t="s">
@@ -4691,7 +4701,7 @@
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="2" t="s">
+      <c r="A45" s="3" t="s">
         <v>410</v>
       </c>
       <c r="B45" s="3" t="s">
@@ -4702,7 +4712,7 @@
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="2" t="s">
+      <c r="A46" s="3" t="s">
         <v>412</v>
       </c>
       <c r="B46" s="3" t="s">
@@ -4713,7 +4723,7 @@
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="2" t="s">
+      <c r="A47" s="3" t="s">
         <v>414</v>
       </c>
       <c r="B47" s="3" t="s">
@@ -4724,7 +4734,7 @@
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="2" t="s">
+      <c r="A48" s="3" t="s">
         <v>416</v>
       </c>
       <c r="B48" s="3" t="s">
@@ -4735,7 +4745,7 @@
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="2" t="s">
+      <c r="A49" s="3" t="s">
         <v>418</v>
       </c>
       <c r="B49" s="3" t="s">
@@ -4746,7 +4756,7 @@
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="2" t="s">
+      <c r="A50" s="3" t="s">
         <v>420</v>
       </c>
       <c r="B50" s="3" t="s">
@@ -4757,7 +4767,7 @@
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="2" t="s">
+      <c r="A51" s="3" t="s">
         <v>422</v>
       </c>
       <c r="B51" s="3" t="s">
@@ -4768,7 +4778,7 @@
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="2" t="s">
+      <c r="A52" s="3" t="s">
         <v>424</v>
       </c>
       <c r="B52" s="3" t="s">
@@ -4779,7 +4789,7 @@
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="2" t="s">
+      <c r="A53" s="3" t="s">
         <v>426</v>
       </c>
       <c r="B53" s="3" t="s">
@@ -4787,7 +4797,7 @@
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="2" t="s">
+      <c r="A54" s="3" t="s">
         <v>428</v>
       </c>
       <c r="B54" s="3" t="s">
@@ -4798,7 +4808,7 @@
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="2" t="s">
+      <c r="A55" s="3" t="s">
         <v>430</v>
       </c>
       <c r="B55" s="3" t="s">
@@ -4809,7 +4819,7 @@
       </c>
     </row>
     <row r="56" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="2" t="s">
+      <c r="A56" s="3" t="s">
         <v>432</v>
       </c>
       <c r="B56" s="3" t="s">
@@ -4820,7 +4830,7 @@
       </c>
     </row>
     <row r="57" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="2" t="s">
+      <c r="A57" s="3" t="s">
         <v>434</v>
       </c>
       <c r="B57" s="3" t="s">
@@ -4831,7 +4841,7 @@
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="2" t="s">
+      <c r="A58" s="3" t="s">
         <v>436</v>
       </c>
       <c r="B58" s="3" t="s">
@@ -4842,7 +4852,7 @@
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="2" t="s">
+      <c r="A59" s="3" t="s">
         <v>438</v>
       </c>
       <c r="B59" s="3" t="s">
@@ -4853,7 +4863,7 @@
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="2" t="s">
+      <c r="A60" s="3" t="s">
         <v>440</v>
       </c>
       <c r="B60" s="3" t="s">
@@ -4864,7 +4874,7 @@
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="2" t="s">
+      <c r="A61" s="3" t="s">
         <v>442</v>
       </c>
       <c r="B61" s="3" t="s">
@@ -4872,7 +4882,7 @@
       </c>
     </row>
     <row r="62" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="2" t="s">
+      <c r="A62" s="3" t="s">
         <v>444</v>
       </c>
       <c r="B62" s="3" t="s">
@@ -4883,7 +4893,7 @@
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="2" t="s">
+      <c r="A63" s="3" t="s">
         <v>446</v>
       </c>
       <c r="B63" s="3" t="s">
@@ -4894,7 +4904,7 @@
       </c>
     </row>
     <row r="64" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="2" t="s">
+      <c r="A64" s="3" t="s">
         <v>448</v>
       </c>
       <c r="B64" s="3" t="s">
@@ -4905,7 +4915,7 @@
       </c>
     </row>
     <row r="65" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="2" t="s">
+      <c r="A65" s="3" t="s">
         <v>450</v>
       </c>
       <c r="B65" s="3" t="s">
@@ -4916,7 +4926,7 @@
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="2" t="s">
+      <c r="A66" s="3" t="s">
         <v>452</v>
       </c>
       <c r="B66" s="3" t="s">
@@ -4927,7 +4937,7 @@
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="2" t="s">
+      <c r="A67" s="3" t="s">
         <v>454</v>
       </c>
       <c r="B67" s="3" t="s">
@@ -4938,7 +4948,7 @@
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="2" t="s">
+      <c r="A68" s="3" t="s">
         <v>456</v>
       </c>
       <c r="B68" s="3" t="s">
@@ -4949,7 +4959,7 @@
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="2" t="s">
+      <c r="A69" s="3" t="s">
         <v>458</v>
       </c>
       <c r="B69" s="3" t="s">
@@ -4960,7 +4970,7 @@
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="2" t="s">
+      <c r="A70" s="3" t="s">
         <v>460</v>
       </c>
       <c r="B70" s="3" t="s">
@@ -4968,7 +4978,7 @@
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="2" t="s">
+      <c r="A71" s="3" t="s">
         <v>462</v>
       </c>
       <c r="B71" s="3" t="s">
@@ -4979,7 +4989,7 @@
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="2" t="s">
+      <c r="A72" s="3" t="s">
         <v>464</v>
       </c>
       <c r="B72" s="3" t="s">
@@ -4990,7 +5000,7 @@
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="2" t="s">
+      <c r="A73" s="3" t="s">
         <v>466</v>
       </c>
       <c r="B73" s="3" t="s">
@@ -5001,7 +5011,7 @@
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="2" t="s">
+      <c r="A74" s="3" t="s">
         <v>468</v>
       </c>
       <c r="B74" s="3" t="s">
@@ -5012,7 +5022,7 @@
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="2" t="s">
+      <c r="A75" s="3" t="s">
         <v>470</v>
       </c>
       <c r="B75" s="3" t="s">
@@ -5023,7 +5033,7 @@
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="2" t="s">
+      <c r="A76" s="3" t="s">
         <v>472</v>
       </c>
       <c r="B76" s="3" t="s">
@@ -5034,7 +5044,7 @@
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="2" t="s">
+      <c r="A77" s="3" t="s">
         <v>474</v>
       </c>
       <c r="B77" s="3" t="s">
@@ -5045,7 +5055,7 @@
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="2" t="s">
+      <c r="A78" s="3" t="s">
         <v>476</v>
       </c>
       <c r="B78" s="3" t="s">
@@ -5075,14 +5085,15 @@
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="103.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="110.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="110.87"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="3" style="2" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>478</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>479</v>
       </c>
       <c r="F1" s="1" t="s">
@@ -5090,10 +5101,10 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="34.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>480</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>481</v>
       </c>
       <c r="F2" s="1" t="s">
@@ -5101,16 +5112,16 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2"/>
+      <c r="A3" s="3"/>
       <c r="F3" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>483</v>
       </c>
       <c r="F4" s="1" t="s">
@@ -5118,10 +5129,10 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>485</v>
       </c>
       <c r="F5" s="1" t="s">
@@ -5129,16 +5140,16 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2"/>
+      <c r="A6" s="3"/>
       <c r="F6" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="3" t="s">
         <v>486</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>487</v>
       </c>
       <c r="F7" s="1" t="s">
@@ -5146,10 +5157,10 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="3" t="s">
         <v>488</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>489</v>
       </c>
       <c r="F8" s="1" t="s">
@@ -5157,10 +5168,10 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="3" t="s">
         <v>490</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>491</v>
       </c>
       <c r="F9" s="1" t="s">
@@ -5168,10 +5179,10 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="3" t="s">
         <v>492</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>493</v>
       </c>
       <c r="F10" s="1" t="s">
@@ -5179,10 +5190,10 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>495</v>
       </c>
       <c r="F11" s="1" t="s">
@@ -5190,10 +5201,10 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="3" t="s">
         <v>496</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="3" t="s">
         <v>497</v>
       </c>
       <c r="F12" s="1" t="s">
@@ -5201,16 +5212,16 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2"/>
+      <c r="A13" s="3"/>
       <c r="F13" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="3" t="s">
         <v>498</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>499</v>
       </c>
       <c r="F14" s="1" t="s">
@@ -5218,10 +5229,10 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="3" t="s">
         <v>500</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="3" t="s">
         <v>501</v>
       </c>
       <c r="F15" s="1" t="s">
@@ -5229,16 +5240,16 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2"/>
+      <c r="A16" s="3"/>
       <c r="F16" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="3" t="s">
         <v>503</v>
       </c>
       <c r="F17" s="1" t="s">
@@ -5246,10 +5257,10 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="3" t="s">
         <v>504</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="3" t="s">
         <v>505</v>
       </c>
       <c r="F18" s="1" t="s">
@@ -5257,16 +5268,16 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2"/>
+      <c r="A19" s="3"/>
       <c r="F19" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="3" t="s">
         <v>506</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="3" t="s">
         <v>507</v>
       </c>
       <c r="F20" s="1" t="s">
@@ -5274,10 +5285,10 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="3" t="s">
         <v>508</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="3" t="s">
         <v>509</v>
       </c>
       <c r="F21" s="1" t="s">
@@ -5285,10 +5296,10 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="3" t="s">
         <v>510</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="3" t="s">
         <v>511</v>
       </c>
       <c r="F22" s="1" t="s">
@@ -5296,10 +5307,10 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="3" t="s">
         <v>512</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="3" t="s">
         <v>513</v>
       </c>
       <c r="F23" s="1" t="s">
@@ -5307,10 +5318,10 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="3" t="s">
         <v>515</v>
       </c>
       <c r="F24" s="1" t="s">
@@ -5318,10 +5329,10 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="3" t="s">
         <v>516</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="3" t="s">
         <v>517</v>
       </c>
       <c r="F25" s="1" t="s">
@@ -5329,10 +5340,10 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="3" t="s">
         <v>518</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="3" t="s">
         <v>519</v>
       </c>
       <c r="F26" s="1" t="s">
@@ -5340,10 +5351,10 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="3" t="s">
         <v>520</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="3" t="s">
         <v>521</v>
       </c>
       <c r="F27" s="1" t="s">
@@ -5351,10 +5362,10 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="34.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="3" t="s">
         <v>522</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="3" t="s">
         <v>523</v>
       </c>
       <c r="F28" s="1" t="s">
@@ -5362,16 +5373,16 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="2"/>
+      <c r="A29" s="3"/>
       <c r="F29" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="3" t="s">
         <v>524</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="3" t="s">
         <v>525</v>
       </c>
       <c r="F30" s="1" t="s">
@@ -5379,10 +5390,10 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="45.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="3" t="s">
         <v>526</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="3" t="s">
         <v>527</v>
       </c>
       <c r="F31" s="1" t="s">
@@ -5390,16 +5401,16 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="2"/>
+      <c r="A32" s="3"/>
       <c r="F32" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="2" t="s">
+      <c r="A33" s="3" t="s">
         <v>528</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="3" t="s">
         <v>529</v>
       </c>
       <c r="F33" s="1" t="s">
@@ -5407,10 +5418,10 @@
       </c>
     </row>
     <row r="34" customFormat="false" ht="34.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="2" t="s">
+      <c r="A34" s="3" t="s">
         <v>530</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="3" t="s">
         <v>531</v>
       </c>
       <c r="F34" s="1" t="s">
@@ -5418,16 +5429,16 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="2"/>
+      <c r="A35" s="3"/>
       <c r="F35" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="2" t="s">
+      <c r="A36" s="3" t="s">
         <v>532</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="3" t="s">
         <v>533</v>
       </c>
       <c r="F36" s="1" t="s">
@@ -5435,10 +5446,10 @@
       </c>
     </row>
     <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="2" t="s">
+      <c r="A37" s="3" t="s">
         <v>534</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B37" s="3" t="s">
         <v>535</v>
       </c>
       <c r="F37" s="1" t="s">
@@ -5446,16 +5457,16 @@
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="2"/>
+      <c r="A38" s="3"/>
       <c r="F38" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="2" t="s">
+      <c r="A39" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" s="3" t="s">
         <v>537</v>
       </c>
       <c r="F39" s="1" t="s">
@@ -5463,10 +5474,10 @@
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="2" t="s">
+      <c r="A40" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B40" s="3" t="s">
         <v>539</v>
       </c>
       <c r="F40" s="1" t="s">
@@ -5474,16 +5485,16 @@
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="2"/>
+      <c r="A41" s="3"/>
       <c r="F41" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="2" t="s">
+      <c r="A42" s="3" t="s">
         <v>540</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B42" s="3" t="s">
         <v>541</v>
       </c>
       <c r="F42" s="1" t="s">
@@ -5491,10 +5502,10 @@
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="2" t="s">
+      <c r="A43" s="3" t="s">
         <v>542</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="B43" s="3" t="s">
         <v>543</v>
       </c>
       <c r="F43" s="1" t="s">
@@ -5502,10 +5513,10 @@
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="2" t="s">
+      <c r="A44" s="3" t="s">
         <v>544</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="B44" s="3" t="s">
         <v>545</v>
       </c>
       <c r="F44" s="1" t="s">
@@ -5513,10 +5524,10 @@
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="2" t="s">
+      <c r="A45" s="3" t="s">
         <v>546</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B45" s="3" t="s">
         <v>547</v>
       </c>
       <c r="F45" s="1" t="s">
@@ -5524,10 +5535,10 @@
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="2" t="s">
+      <c r="A46" s="3" t="s">
         <v>548</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B46" s="3" t="s">
         <v>549</v>
       </c>
       <c r="F46" s="1" t="s">
@@ -5535,10 +5546,10 @@
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="2" t="s">
+      <c r="A47" s="3" t="s">
         <v>550</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B47" s="3" t="s">
         <v>551</v>
       </c>
       <c r="F47" s="1" t="s">
@@ -5546,10 +5557,10 @@
       </c>
     </row>
     <row r="48" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="2" t="s">
+      <c r="A48" s="3" t="s">
         <v>552</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B48" s="3" t="s">
         <v>553</v>
       </c>
       <c r="F48" s="1" t="s">
@@ -5557,16 +5568,16 @@
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="2"/>
+      <c r="A49" s="3"/>
       <c r="F49" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="2" t="s">
+      <c r="A50" s="3" t="s">
         <v>554</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="B50" s="3" t="s">
         <v>555</v>
       </c>
       <c r="F50" s="1" t="s">
@@ -5574,10 +5585,10 @@
       </c>
     </row>
     <row r="51" customFormat="false" ht="34.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="2" t="s">
+      <c r="A51" s="3" t="s">
         <v>556</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="B51" s="3" t="s">
         <v>557</v>
       </c>
       <c r="F51" s="1" t="s">
@@ -5585,16 +5596,16 @@
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="2"/>
+      <c r="A52" s="3"/>
       <c r="F52" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="2" t="s">
+      <c r="A53" s="3" t="s">
         <v>558</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="B53" s="3" t="s">
         <v>559</v>
       </c>
       <c r="F53" s="1" t="s">
@@ -5602,10 +5613,10 @@
       </c>
     </row>
     <row r="54" customFormat="false" ht="45.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="2" t="s">
+      <c r="A54" s="3" t="s">
         <v>560</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="B54" s="3" t="s">
         <v>561</v>
       </c>
       <c r="F54" s="1" t="s">
@@ -5613,16 +5624,16 @@
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="2"/>
+      <c r="A55" s="3"/>
       <c r="F55" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="2" t="s">
+      <c r="A56" s="3" t="s">
         <v>562</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="B56" s="3" t="s">
         <v>563</v>
       </c>
       <c r="F56" s="1" t="s">
@@ -5630,10 +5641,10 @@
       </c>
     </row>
     <row r="57" customFormat="false" ht="34.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="2" t="s">
+      <c r="A57" s="3" t="s">
         <v>564</v>
       </c>
-      <c r="B57" s="2" t="s">
+      <c r="B57" s="3" t="s">
         <v>565</v>
       </c>
       <c r="F57" s="1" t="s">
@@ -5641,16 +5652,16 @@
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="2"/>
+      <c r="A58" s="3"/>
       <c r="F58" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="2" t="s">
+      <c r="A59" s="3" t="s">
         <v>566</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="B59" s="3" t="s">
         <v>567</v>
       </c>
       <c r="F59" s="1" t="s">
@@ -5658,10 +5669,10 @@
       </c>
     </row>
     <row r="60" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="2" t="s">
+      <c r="A60" s="3" t="s">
         <v>568</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="B60" s="3" t="s">
         <v>569</v>
       </c>
       <c r="F60" s="1" t="s">
@@ -5669,10 +5680,10 @@
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="2" t="s">
+      <c r="A61" s="3" t="s">
         <v>570</v>
       </c>
-      <c r="B61" s="2" t="s">
+      <c r="B61" s="3" t="s">
         <v>571</v>
       </c>
       <c r="F61" s="1" t="s">
@@ -5680,10 +5691,10 @@
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="2" t="s">
+      <c r="A62" s="3" t="s">
         <v>572</v>
       </c>
-      <c r="B62" s="2" t="s">
+      <c r="B62" s="3" t="s">
         <v>573</v>
       </c>
       <c r="F62" s="1" t="s">
@@ -5691,10 +5702,10 @@
       </c>
     </row>
     <row r="63" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="2" t="s">
+      <c r="A63" s="3" t="s">
         <v>574</v>
       </c>
-      <c r="B63" s="2" t="s">
+      <c r="B63" s="3" t="s">
         <v>575</v>
       </c>
       <c r="F63" s="1" t="s">
@@ -5702,16 +5713,16 @@
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="2"/>
+      <c r="A64" s="3"/>
       <c r="F64" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="2" t="s">
+      <c r="A65" s="3" t="s">
         <v>576</v>
       </c>
-      <c r="B65" s="2" t="s">
+      <c r="B65" s="3" t="s">
         <v>577</v>
       </c>
       <c r="F65" s="1" t="s">
@@ -5719,10 +5730,10 @@
       </c>
     </row>
     <row r="66" customFormat="false" ht="34.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="2" t="s">
+      <c r="A66" s="3" t="s">
         <v>578</v>
       </c>
-      <c r="B66" s="2" t="s">
+      <c r="B66" s="3" t="s">
         <v>579</v>
       </c>
       <c r="F66" s="1" t="s">
@@ -5730,16 +5741,16 @@
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="2"/>
+      <c r="A67" s="3"/>
       <c r="F67" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="2" t="s">
+      <c r="A68" s="3" t="s">
         <v>580</v>
       </c>
-      <c r="B68" s="2" t="s">
+      <c r="B68" s="3" t="s">
         <v>581</v>
       </c>
       <c r="F68" s="1" t="s">
@@ -5747,10 +5758,10 @@
       </c>
     </row>
     <row r="69" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="2" t="s">
+      <c r="A69" s="3" t="s">
         <v>582</v>
       </c>
-      <c r="B69" s="2" t="s">
+      <c r="B69" s="3" t="s">
         <v>583</v>
       </c>
       <c r="F69" s="1" t="s">
@@ -5758,16 +5769,16 @@
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="2"/>
+      <c r="A70" s="3"/>
       <c r="F70" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="2" t="s">
+      <c r="A71" s="3" t="s">
         <v>584</v>
       </c>
-      <c r="B71" s="2" t="s">
+      <c r="B71" s="3" t="s">
         <v>585</v>
       </c>
       <c r="F71" s="1" t="s">
@@ -5775,10 +5786,10 @@
       </c>
     </row>
     <row r="72" customFormat="false" ht="45.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="2" t="s">
+      <c r="A72" s="3" t="s">
         <v>586</v>
       </c>
-      <c r="B72" s="2" t="s">
+      <c r="B72" s="3" t="s">
         <v>587</v>
       </c>
       <c r="F72" s="1" t="s">
@@ -5791,10 +5802,10 @@
       </c>
     </row>
     <row r="74" customFormat="false" ht="57.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="2" t="s">
+      <c r="A74" s="3" t="s">
         <v>588</v>
       </c>
-      <c r="B74" s="2" t="s">
+      <c r="B74" s="3" t="s">
         <v>589</v>
       </c>
       <c r="F74" s="1" t="s">
@@ -5802,16 +5813,16 @@
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="2"/>
+      <c r="A75" s="3"/>
       <c r="F75" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="57.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="2" t="s">
+      <c r="A76" s="3" t="s">
         <v>590</v>
       </c>
-      <c r="B76" s="2" t="s">
+      <c r="B76" s="3" t="s">
         <v>591</v>
       </c>
       <c r="F76" s="1" t="s">
@@ -5819,16 +5830,16 @@
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="2"/>
+      <c r="A77" s="3"/>
       <c r="F77" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="57.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="2" t="s">
+      <c r="A78" s="3" t="s">
         <v>592</v>
       </c>
-      <c r="B78" s="2" t="s">
+      <c r="B78" s="3" t="s">
         <v>593</v>
       </c>
       <c r="F78" s="1" t="s">
@@ -5836,16 +5847,16 @@
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="2"/>
+      <c r="A79" s="3"/>
       <c r="F79" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="45.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="2" t="s">
+      <c r="A80" s="3" t="s">
         <v>594</v>
       </c>
-      <c r="B80" s="2" t="s">
+      <c r="B80" s="3" t="s">
         <v>595</v>
       </c>
       <c r="F80" s="1" t="s">
@@ -5853,16 +5864,16 @@
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="2"/>
+      <c r="A81" s="3"/>
       <c r="F81" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="45.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="2" t="s">
+      <c r="A82" s="3" t="s">
         <v>596</v>
       </c>
-      <c r="B82" s="2" t="s">
+      <c r="B82" s="3" t="s">
         <v>597</v>
       </c>
       <c r="F82" s="1" t="s">
@@ -5870,16 +5881,16 @@
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="2"/>
+      <c r="A83" s="3"/>
       <c r="F83" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="2" t="s">
+      <c r="A84" s="3" t="s">
         <v>598</v>
       </c>
-      <c r="B84" s="2" t="s">
+      <c r="B84" s="3" t="s">
         <v>599</v>
       </c>
       <c r="F84" s="1" t="s">
@@ -5887,16 +5898,16 @@
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="2"/>
+      <c r="A85" s="3"/>
       <c r="F85" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="45.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="2" t="s">
+      <c r="A86" s="3" t="s">
         <v>600</v>
       </c>
-      <c r="B86" s="2" t="s">
+      <c r="B86" s="3" t="s">
         <v>601</v>
       </c>
       <c r="F86" s="1" t="s">
@@ -5904,56 +5915,56 @@
       </c>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="2"/>
+      <c r="A87" s="3"/>
       <c r="F87" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="34.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="2" t="s">
+      <c r="A88" s="3" t="s">
         <v>602</v>
       </c>
-      <c r="B88" s="2" t="s">
+      <c r="B88" s="3" t="s">
         <v>603</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="2" t="s">
+      <c r="A89" s="3" t="s">
         <v>604</v>
       </c>
-      <c r="B89" s="2" t="s">
+      <c r="B89" s="3" t="s">
         <v>605</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="2" t="s">
+      <c r="A90" s="3" t="s">
         <v>606</v>
       </c>
-      <c r="B90" s="2" t="s">
+      <c r="B90" s="3" t="s">
         <v>607</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="2" t="s">
+      <c r="A91" s="3" t="s">
         <v>608</v>
       </c>
-      <c r="B91" s="2" t="s">
+      <c r="B91" s="3" t="s">
         <v>609</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="2" t="s">
+      <c r="A92" s="3" t="s">
         <v>610</v>
       </c>
-      <c r="B92" s="2" t="s">
+      <c r="B92" s="3" t="s">
         <v>611</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="2" t="s">
+      <c r="A93" s="3" t="s">
         <v>612</v>
       </c>
-      <c r="B93" s="2" t="s">
+      <c r="B93" s="3" t="s">
         <v>613</v>
       </c>
       <c r="F93" s="1" t="s">
@@ -5961,74 +5972,74 @@
       </c>
     </row>
     <row r="94" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="2" t="s">
+      <c r="A94" s="3" t="s">
         <v>614</v>
       </c>
-      <c r="B94" s="2" t="s">
+      <c r="B94" s="3" t="s">
         <v>615</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="2" t="s">
+      <c r="A95" s="3" t="s">
         <v>616</v>
       </c>
-      <c r="B95" s="2" t="s">
+      <c r="B95" s="3" t="s">
         <v>617</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="2" t="s">
+      <c r="A96" s="3" t="s">
         <v>618</v>
       </c>
-      <c r="B96" s="2" t="s">
+      <c r="B96" s="3" t="s">
         <v>619</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="2" t="s">
+      <c r="A97" s="3" t="s">
         <v>620</v>
       </c>
-      <c r="B97" s="2" t="s">
+      <c r="B97" s="3" t="s">
         <v>621</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="2" t="s">
+      <c r="A98" s="3" t="s">
         <v>622</v>
       </c>
-      <c r="B98" s="2" t="s">
+      <c r="B98" s="3" t="s">
         <v>623</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="2" t="s">
+      <c r="A99" s="3" t="s">
         <v>624</v>
       </c>
-      <c r="B99" s="2" t="s">
+      <c r="B99" s="3" t="s">
         <v>625</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="2" t="s">
+      <c r="A100" s="3" t="s">
         <v>626</v>
       </c>
-      <c r="B100" s="2" t="s">
+      <c r="B100" s="3" t="s">
         <v>627</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="2" t="s">
+      <c r="A101" s="3" t="s">
         <v>628</v>
       </c>
-      <c r="B101" s="2" t="s">
+      <c r="B101" s="3" t="s">
         <v>629</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="34.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="2" t="s">
+      <c r="A102" s="3" t="s">
         <v>630</v>
       </c>
-      <c r="B102" s="2" t="s">
+      <c r="B102" s="3" t="s">
         <v>631</v>
       </c>
       <c r="F102" s="1" t="s">
@@ -6036,18 +6047,18 @@
       </c>
     </row>
     <row r="103" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="2" t="s">
+      <c r="A103" s="3" t="s">
         <v>632</v>
       </c>
-      <c r="B103" s="2" t="s">
+      <c r="B103" s="3" t="s">
         <v>633</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="2" t="s">
+      <c r="A104" s="3" t="s">
         <v>634</v>
       </c>
-      <c r="B104" s="2" t="s">
+      <c r="B104" s="3" t="s">
         <v>635</v>
       </c>
       <c r="F104" s="1" t="s">
@@ -6055,10 +6066,10 @@
       </c>
     </row>
     <row r="105" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="2" t="s">
+      <c r="A105" s="3" t="s">
         <v>636</v>
       </c>
-      <c r="B105" s="2" t="s">
+      <c r="B105" s="3" t="s">
         <v>637</v>
       </c>
       <c r="F105" s="1" t="s">
@@ -6066,10 +6077,10 @@
       </c>
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="2" t="s">
+      <c r="A106" s="3" t="s">
         <v>638</v>
       </c>
-      <c r="B106" s="2" t="s">
+      <c r="B106" s="3" t="s">
         <v>639</v>
       </c>
       <c r="F106" s="1" t="s">
@@ -6077,10 +6088,10 @@
       </c>
     </row>
     <row r="107" customFormat="false" ht="34.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="2" t="s">
+      <c r="A107" s="3" t="s">
         <v>640</v>
       </c>
-      <c r="B107" s="2" t="s">
+      <c r="B107" s="3" t="s">
         <v>641</v>
       </c>
       <c r="F107" s="1" t="s">
@@ -6088,10 +6099,10 @@
       </c>
     </row>
     <row r="108" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="2" t="s">
+      <c r="A108" s="3" t="s">
         <v>642</v>
       </c>
-      <c r="B108" s="2" t="s">
+      <c r="B108" s="3" t="s">
         <v>643</v>
       </c>
       <c r="F108" s="1" t="s">
@@ -6099,10 +6110,10 @@
       </c>
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="2" t="s">
+      <c r="A109" s="3" t="s">
         <v>644</v>
       </c>
-      <c r="B109" s="2" t="s">
+      <c r="B109" s="3" t="s">
         <v>645</v>
       </c>
       <c r="F109" s="1" t="s">
@@ -6110,10 +6121,10 @@
       </c>
     </row>
     <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="2" t="s">
+      <c r="A110" s="3" t="s">
         <v>646</v>
       </c>
-      <c r="B110" s="2" t="s">
+      <c r="B110" s="3" t="s">
         <v>647</v>
       </c>
       <c r="F110" s="1" t="s">
@@ -6121,18 +6132,18 @@
       </c>
     </row>
     <row r="111" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="2" t="s">
+      <c r="A111" s="3" t="s">
         <v>648</v>
       </c>
-      <c r="B111" s="2" t="s">
+      <c r="B111" s="3" t="s">
         <v>649</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="2" t="s">
+      <c r="A112" s="3" t="s">
         <v>650</v>
       </c>
-      <c r="B112" s="2" t="s">
+      <c r="B112" s="3" t="s">
         <v>651</v>
       </c>
       <c r="F112" s="1" t="s">
@@ -6140,10 +6151,10 @@
       </c>
     </row>
     <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="2" t="s">
+      <c r="A113" s="3" t="s">
         <v>652</v>
       </c>
-      <c r="B113" s="2" t="s">
+      <c r="B113" s="3" t="s">
         <v>653</v>
       </c>
       <c r="F113" s="1" t="s">
@@ -6151,10 +6162,10 @@
       </c>
     </row>
     <row r="114" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="2" t="s">
+      <c r="A114" s="3" t="s">
         <v>654</v>
       </c>
-      <c r="B114" s="2" t="s">
+      <c r="B114" s="3" t="s">
         <v>655</v>
       </c>
       <c r="F114" s="1" t="s">
@@ -6162,10 +6173,10 @@
       </c>
     </row>
     <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="2" t="s">
+      <c r="A115" s="3" t="s">
         <v>656</v>
       </c>
-      <c r="B115" s="2" t="s">
+      <c r="B115" s="3" t="s">
         <v>657</v>
       </c>
       <c r="F115" s="1" t="s">
@@ -6173,10 +6184,10 @@
       </c>
     </row>
     <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="2" t="s">
+      <c r="A116" s="3" t="s">
         <v>658</v>
       </c>
-      <c r="B116" s="2" t="s">
+      <c r="B116" s="3" t="s">
         <v>659</v>
       </c>
       <c r="F116" s="1" t="s">
@@ -6184,18 +6195,18 @@
       </c>
     </row>
     <row r="117" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="2" t="s">
+      <c r="A117" s="3" t="s">
         <v>660</v>
       </c>
-      <c r="B117" s="2" t="s">
+      <c r="B117" s="3" t="s">
         <v>661</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="2" t="s">
+      <c r="A118" s="3" t="s">
         <v>662</v>
       </c>
-      <c r="B118" s="2" t="s">
+      <c r="B118" s="3" t="s">
         <v>663</v>
       </c>
       <c r="F118" s="1" t="s">
@@ -6203,10 +6214,10 @@
       </c>
     </row>
     <row r="119" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="2" t="s">
+      <c r="A119" s="3" t="s">
         <v>664</v>
       </c>
-      <c r="B119" s="2" t="s">
+      <c r="B119" s="3" t="s">
         <v>665</v>
       </c>
       <c r="F119" s="1" t="s">
@@ -6214,10 +6225,10 @@
       </c>
     </row>
     <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="2" t="s">
+      <c r="A120" s="3" t="s">
         <v>666</v>
       </c>
-      <c r="B120" s="2" t="s">
+      <c r="B120" s="3" t="s">
         <v>667</v>
       </c>
       <c r="F120" s="1" t="s">
@@ -6225,10 +6236,10 @@
       </c>
     </row>
     <row r="121" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="2" t="s">
+      <c r="A121" s="3" t="s">
         <v>668</v>
       </c>
-      <c r="B121" s="2" t="s">
+      <c r="B121" s="3" t="s">
         <v>669</v>
       </c>
       <c r="F121" s="1" t="s">
@@ -6236,18 +6247,18 @@
       </c>
     </row>
     <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="2" t="s">
+      <c r="A122" s="3" t="s">
         <v>670</v>
       </c>
-      <c r="B122" s="2" t="s">
+      <c r="B122" s="3" t="s">
         <v>671</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="2" t="s">
+      <c r="A123" s="3" t="s">
         <v>672</v>
       </c>
-      <c r="B123" s="2" t="s">
+      <c r="B123" s="3" t="s">
         <v>673</v>
       </c>
       <c r="F123" s="1" t="s">
@@ -6255,10 +6266,10 @@
       </c>
     </row>
     <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="2" t="s">
+      <c r="A124" s="3" t="s">
         <v>674</v>
       </c>
-      <c r="B124" s="2" t="s">
+      <c r="B124" s="3" t="s">
         <v>675</v>
       </c>
       <c r="F124" s="1" t="s">
@@ -6266,10 +6277,10 @@
       </c>
     </row>
     <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="2" t="s">
+      <c r="A125" s="3" t="s">
         <v>676</v>
       </c>
-      <c r="B125" s="2" t="s">
+      <c r="B125" s="3" t="s">
         <v>677</v>
       </c>
       <c r="F125" s="1" t="s">
@@ -6277,10 +6288,10 @@
       </c>
     </row>
     <row r="126" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="2" t="s">
+      <c r="A126" s="3" t="s">
         <v>678</v>
       </c>
-      <c r="B126" s="2" t="s">
+      <c r="B126" s="3" t="s">
         <v>679</v>
       </c>
       <c r="F126" s="1" t="s">
@@ -6288,18 +6299,18 @@
       </c>
     </row>
     <row r="127" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="2" t="s">
+      <c r="A127" s="3" t="s">
         <v>680</v>
       </c>
-      <c r="B127" s="2" t="s">
+      <c r="B127" s="3" t="s">
         <v>681</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="2" t="s">
+      <c r="A128" s="3" t="s">
         <v>682</v>
       </c>
-      <c r="B128" s="2" t="s">
+      <c r="B128" s="3" t="s">
         <v>683</v>
       </c>
       <c r="F128" s="1" t="s">
@@ -6307,10 +6318,10 @@
       </c>
     </row>
     <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="2" t="s">
+      <c r="A129" s="3" t="s">
         <v>684</v>
       </c>
-      <c r="B129" s="2" t="s">
+      <c r="B129" s="3" t="s">
         <v>685</v>
       </c>
       <c r="F129" s="1" t="s">
@@ -6318,10 +6329,10 @@
       </c>
     </row>
     <row r="130" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="2" t="s">
+      <c r="A130" s="3" t="s">
         <v>686</v>
       </c>
-      <c r="B130" s="2" t="s">
+      <c r="B130" s="3" t="s">
         <v>687</v>
       </c>
       <c r="F130" s="1" t="s">
@@ -6329,18 +6340,18 @@
       </c>
     </row>
     <row r="131" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="2" t="s">
+      <c r="A131" s="3" t="s">
         <v>688</v>
       </c>
-      <c r="B131" s="2" t="s">
+      <c r="B131" s="3" t="s">
         <v>689</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="2" t="s">
+      <c r="A132" s="3" t="s">
         <v>690</v>
       </c>
-      <c r="B132" s="2" t="s">
+      <c r="B132" s="3" t="s">
         <v>691</v>
       </c>
       <c r="F132" s="1" t="s">
@@ -6348,10 +6359,10 @@
       </c>
     </row>
     <row r="133" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="2" t="s">
+      <c r="A133" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="B133" s="2" t="s">
+      <c r="B133" s="3" t="s">
         <v>693</v>
       </c>
       <c r="F133" s="1" t="s">
@@ -6359,10 +6370,10 @@
       </c>
     </row>
     <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="2" t="s">
+      <c r="A134" s="3" t="s">
         <v>694</v>
       </c>
-      <c r="B134" s="2" t="s">
+      <c r="B134" s="3" t="s">
         <v>695</v>
       </c>
       <c r="F134" s="1" t="s">
@@ -6370,10 +6381,10 @@
       </c>
     </row>
     <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="2" t="s">
+      <c r="A135" s="3" t="s">
         <v>696</v>
       </c>
-      <c r="B135" s="2" t="s">
+      <c r="B135" s="3" t="s">
         <v>697</v>
       </c>
       <c r="F135" s="1" t="s">
@@ -6381,18 +6392,18 @@
       </c>
     </row>
     <row r="136" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="2" t="s">
+      <c r="A136" s="3" t="s">
         <v>698</v>
       </c>
-      <c r="B136" s="2" t="s">
+      <c r="B136" s="3" t="s">
         <v>699</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="2" t="s">
+      <c r="A137" s="3" t="s">
         <v>700</v>
       </c>
-      <c r="B137" s="2" t="s">
+      <c r="B137" s="3" t="s">
         <v>701</v>
       </c>
       <c r="F137" s="1" t="s">
@@ -6400,10 +6411,10 @@
       </c>
     </row>
     <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="2" t="s">
+      <c r="A138" s="3" t="s">
         <v>702</v>
       </c>
-      <c r="B138" s="2" t="s">
+      <c r="B138" s="3" t="s">
         <v>703</v>
       </c>
       <c r="F138" s="1" t="s">
@@ -6411,10 +6422,10 @@
       </c>
     </row>
     <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="2" t="s">
+      <c r="A139" s="3" t="s">
         <v>704</v>
       </c>
-      <c r="B139" s="2" t="s">
+      <c r="B139" s="3" t="s">
         <v>705</v>
       </c>
       <c r="F139" s="1" t="s">
@@ -6422,10 +6433,10 @@
       </c>
     </row>
     <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="2" t="s">
+      <c r="A140" s="3" t="s">
         <v>706</v>
       </c>
-      <c r="B140" s="2" t="s">
+      <c r="B140" s="3" t="s">
         <v>707</v>
       </c>
       <c r="F140" s="1" t="s">
@@ -6433,18 +6444,18 @@
       </c>
     </row>
     <row r="141" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="2" t="s">
+      <c r="A141" s="3" t="s">
         <v>708</v>
       </c>
-      <c r="B141" s="2" t="s">
+      <c r="B141" s="3" t="s">
         <v>709</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="2" t="s">
+      <c r="A142" s="3" t="s">
         <v>710</v>
       </c>
-      <c r="B142" s="2" t="s">
+      <c r="B142" s="3" t="s">
         <v>711</v>
       </c>
       <c r="F142" s="1" t="s">
@@ -6452,10 +6463,10 @@
       </c>
     </row>
     <row r="143" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="2" t="s">
+      <c r="A143" s="3" t="s">
         <v>712</v>
       </c>
-      <c r="B143" s="2" t="s">
+      <c r="B143" s="3" t="s">
         <v>713</v>
       </c>
       <c r="F143" s="1" t="s">
@@ -6463,10 +6474,10 @@
       </c>
     </row>
     <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="2" t="s">
+      <c r="A144" s="3" t="s">
         <v>714</v>
       </c>
-      <c r="B144" s="2" t="s">
+      <c r="B144" s="3" t="s">
         <v>715</v>
       </c>
       <c r="F144" s="1" t="s">
@@ -6474,10 +6485,10 @@
       </c>
     </row>
     <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="2" t="s">
+      <c r="A145" s="3" t="s">
         <v>716</v>
       </c>
-      <c r="B145" s="2" t="s">
+      <c r="B145" s="3" t="s">
         <v>717</v>
       </c>
       <c r="F145" s="1" t="s">
@@ -6485,18 +6496,18 @@
       </c>
     </row>
     <row r="146" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="2" t="s">
+      <c r="A146" s="3" t="s">
         <v>718</v>
       </c>
-      <c r="B146" s="2" t="s">
+      <c r="B146" s="3" t="s">
         <v>719</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="2" t="s">
+      <c r="A147" s="3" t="s">
         <v>720</v>
       </c>
-      <c r="B147" s="2" t="s">
+      <c r="B147" s="3" t="s">
         <v>721</v>
       </c>
       <c r="F147" s="1" t="s">
@@ -6504,10 +6515,10 @@
       </c>
     </row>
     <row r="148" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="2" t="s">
+      <c r="A148" s="3" t="s">
         <v>722</v>
       </c>
-      <c r="B148" s="2" t="s">
+      <c r="B148" s="3" t="s">
         <v>723</v>
       </c>
       <c r="F148" s="1" t="s">
